--- a/database/event/8249/event_8249_evp_summary.xlsx
+++ b/database/event/8249/event_8249_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.6786</v>
+        <v>3.6241</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0059</v>
+        <v>1.9762</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0647</v>
+        <v>0.9999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6786</v>
+        <v>3.6241</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6786</v>
+        <v>3.6241</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6786</v>
+        <v>3.6241</v>
       </c>
       <c r="I2" t="n">
         <v>3.7476</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.4639</v>
+        <v>3.4125</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8888</v>
+        <v>1.8608</v>
       </c>
       <c r="D3" t="n">
-        <v>0.978</v>
+        <v>0.9156</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4639</v>
+        <v>3.4125</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4639</v>
+        <v>3.4125</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4639</v>
+        <v>3.4125</v>
       </c>
       <c r="I3" t="n">
         <v>3.5288</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4347</v>
+        <v>3.3837</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8729</v>
+        <v>1.8451</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9042</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4347</v>
+        <v>3.3837</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4347</v>
+        <v>3.3837</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4347</v>
+        <v>3.3837</v>
       </c>
       <c r="I4" t="n">
         <v>3.4991</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4346</v>
+        <v>3.3837</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8728</v>
+        <v>1.8451</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9661</v>
+        <v>0.9042</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4346</v>
+        <v>3.3837</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4346</v>
+        <v>3.3837</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4346</v>
+        <v>3.3837</v>
       </c>
       <c r="I5" t="n">
         <v>3.499</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0521</v>
+        <v>3.0068</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6643</v>
+        <v>1.6396</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8116</v>
+        <v>0.754</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0521</v>
+        <v>3.0068</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0521</v>
+        <v>3.0068</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0521</v>
+        <v>3.0068</v>
       </c>
       <c r="I6" t="n">
         <v>3.1093</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9682</v>
+        <v>2.9241</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6185</v>
+        <v>1.5945</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7211</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9682</v>
+        <v>2.9241</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9682</v>
+        <v>2.9241</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9682</v>
+        <v>2.9241</v>
       </c>
       <c r="I7" t="n">
         <v>3.0238</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.744</v>
+        <v>2.7033</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4963</v>
+        <v>1.4741</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6872</v>
+        <v>0.6331</v>
       </c>
       <c r="E8" t="n">
-        <v>2.744</v>
+        <v>2.7033</v>
       </c>
       <c r="F8" t="n">
-        <v>2.744</v>
+        <v>2.7033</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.744</v>
+        <v>2.7033</v>
       </c>
       <c r="I8" t="n">
         <v>2.7955</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.719</v>
+        <v>2.6787</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4826</v>
+        <v>1.4607</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6771</v>
+        <v>0.6233</v>
       </c>
       <c r="E9" t="n">
-        <v>2.719</v>
+        <v>2.6787</v>
       </c>
       <c r="F9" t="n">
-        <v>2.719</v>
+        <v>2.6787</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.719</v>
+        <v>2.6787</v>
       </c>
       <c r="I9" t="n">
         <v>2.77</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6789</v>
+        <v>2.6391</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4608</v>
+        <v>1.4391</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6609</v>
+        <v>0.6075</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6789</v>
+        <v>2.6391</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6789</v>
+        <v>2.6391</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6789</v>
+        <v>2.6391</v>
       </c>
       <c r="I10" t="n">
         <v>2.7291</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6726</v>
+        <v>2.633</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4573</v>
+        <v>1.4357</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6583</v>
+        <v>0.6051</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6726</v>
+        <v>2.633</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6726</v>
+        <v>2.633</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6726</v>
+        <v>2.633</v>
       </c>
       <c r="I11" t="n">
         <v>2.7228</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5571</v>
+        <v>2.5191</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3944</v>
+        <v>1.3736</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6116</v>
+        <v>0.5597</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5571</v>
+        <v>2.5191</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5571</v>
+        <v>2.5191</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5571</v>
+        <v>2.5191</v>
       </c>
       <c r="I12" t="n">
         <v>2.605</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5364</v>
+        <v>2.4988</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3831</v>
+        <v>1.3626</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.5516</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5364</v>
+        <v>2.4988</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5364</v>
+        <v>2.4988</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5364</v>
+        <v>2.4988</v>
       </c>
       <c r="I13" t="n">
         <v>2.584</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3042</v>
+        <v>2.2701</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2565</v>
+        <v>1.2379</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5095</v>
+        <v>0.4605</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3042</v>
+        <v>2.2701</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3042</v>
+        <v>2.2701</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3042</v>
+        <v>2.2701</v>
       </c>
       <c r="I14" t="n">
         <v>2.3474</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2604</v>
+        <v>2.2269</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2326</v>
+        <v>1.2143</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4918</v>
+        <v>0.4433</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2604</v>
+        <v>2.2269</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2604</v>
+        <v>2.2269</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2604</v>
+        <v>2.2269</v>
       </c>
       <c r="I15" t="n">
         <v>2.3028</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2273</v>
+        <v>2.1943</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2145</v>
+        <v>1.1965</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4784</v>
+        <v>0.4303</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2273</v>
+        <v>2.1943</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2273</v>
+        <v>2.1943</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2273</v>
+        <v>2.1943</v>
       </c>
       <c r="I16" t="n">
         <v>2.2691</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0759</v>
+        <v>2.0451</v>
       </c>
       <c r="C17" t="n">
-        <v>1.132</v>
+        <v>1.1152</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4173</v>
+        <v>0.3709</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0759</v>
+        <v>2.0451</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0759</v>
+        <v>2.0451</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0759</v>
+        <v>2.0451</v>
       </c>
       <c r="I17" t="n">
         <v>2.1148</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0644</v>
+        <v>2.0337</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1257</v>
+        <v>1.109</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4126</v>
+        <v>0.3663</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0644</v>
+        <v>2.0337</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0644</v>
+        <v>2.0337</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0644</v>
+        <v>2.0337</v>
       </c>
       <c r="I18" t="n">
         <v>2.1031</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0217</v>
+        <v>1.9917</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1024</v>
+        <v>1.086</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3954</v>
+        <v>0.3496</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0217</v>
+        <v>1.9917</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0217</v>
+        <v>1.9917</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0217</v>
+        <v>1.9917</v>
       </c>
       <c r="I19" t="n">
         <v>2.0596</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9971</v>
+        <v>1.9695</v>
       </c>
       <c r="C20" t="n">
-        <v>1.089</v>
+        <v>1.0739</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3854</v>
+        <v>0.3407</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9971</v>
+        <v>1.9695</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9971</v>
+        <v>1.9695</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9971</v>
+        <v>1.9695</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0345</v>
+        <v>2.0197</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0345</v>
+        <v>2.0197</v>
       </c>
       <c r="N20" t="n">
-        <v>181</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9917</v>
+        <v>1.9674</v>
       </c>
       <c r="C21" t="n">
-        <v>1.086</v>
+        <v>1.0728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3832</v>
+        <v>0.3399</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9917</v>
+        <v>1.9674</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9917</v>
+        <v>1.9674</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9917</v>
+        <v>1.9674</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0197</v>
+        <v>2.0345</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0197</v>
+        <v>2.0345</v>
       </c>
       <c r="N21" t="n">
-        <v>143</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22">
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.898</v>
+        <v>1.8699</v>
       </c>
       <c r="C22" t="n">
-        <v>1.035</v>
+        <v>1.0196</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3454</v>
+        <v>0.3011</v>
       </c>
       <c r="E22" t="n">
-        <v>1.898</v>
+        <v>1.8699</v>
       </c>
       <c r="F22" t="n">
-        <v>1.898</v>
+        <v>1.8699</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.898</v>
+        <v>1.8699</v>
       </c>
       <c r="I22" t="n">
         <v>1.9336</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7685</v>
+        <v>1.7423</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9643</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2931</v>
+        <v>0.2502</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7685</v>
+        <v>1.7423</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7685</v>
+        <v>1.7423</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7685</v>
+        <v>1.7423</v>
       </c>
       <c r="I23" t="n">
         <v>1.8017</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7182</v>
+        <v>1.6927</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9369</v>
+        <v>0.923</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2728</v>
+        <v>0.2305</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7182</v>
+        <v>1.6927</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7182</v>
+        <v>1.6927</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7182</v>
+        <v>1.6927</v>
       </c>
       <c r="I24" t="n">
         <v>1.7504</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7009</v>
+        <v>1.6757</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9275</v>
+        <v>0.9137</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2658</v>
+        <v>0.2237</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7009</v>
+        <v>1.6757</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7009</v>
+        <v>1.6757</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7009</v>
+        <v>1.6757</v>
       </c>
       <c r="I25" t="n">
         <v>1.7328</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6562</v>
+        <v>1.6438</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9031</v>
+        <v>0.8963</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2477</v>
+        <v>0.211</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6562</v>
+        <v>1.6438</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6562</v>
+        <v>1.6438</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6562</v>
+        <v>1.6438</v>
       </c>
       <c r="I26" t="n">
         <v>1.6716</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.4801</v>
+        <v>1.4581</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8071</v>
+        <v>0.7951</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1766</v>
+        <v>0.137</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4801</v>
+        <v>1.4581</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4801</v>
+        <v>1.4581</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4801</v>
+        <v>1.4581</v>
       </c>
       <c r="I27" t="n">
         <v>1.5078</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3261</v>
+        <v>1.3064</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7231</v>
+        <v>0.7124</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1144</v>
+        <v>0.0766</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3261</v>
+        <v>1.3064</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3261</v>
+        <v>1.3064</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3261</v>
+        <v>1.3064</v>
       </c>
       <c r="I28" t="n">
         <v>1.351</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2393</v>
+        <v>1.2209</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6758</v>
+        <v>0.6657</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0793</v>
+        <v>0.0425</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2393</v>
+        <v>1.2209</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2393</v>
+        <v>1.2209</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2393</v>
+        <v>1.2209</v>
       </c>
       <c r="I29" t="n">
         <v>1.2625</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.121</v>
+        <v>1.1044</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6113</v>
+        <v>0.6022</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0315</v>
+        <v>-0.0039</v>
       </c>
       <c r="E30" t="n">
-        <v>1.121</v>
+        <v>1.1044</v>
       </c>
       <c r="F30" t="n">
-        <v>1.121</v>
+        <v>1.1044</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.121</v>
+        <v>1.1044</v>
       </c>
       <c r="I30" t="n">
         <v>1.142</v>
@@ -1836,7 +1836,7 @@
         <v>0.5387</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0222</v>
+        <v>-0.0503</v>
       </c>
       <c r="E31" t="n">
         <v>0.988</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9831</v>
+        <v>0.9757</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5361</v>
+        <v>0.532</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0242</v>
+        <v>-0.0552</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9831</v>
+        <v>0.9757</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9831</v>
+        <v>0.9757</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9831</v>
+        <v>0.9757</v>
       </c>
       <c r="I32" t="n">
         <v>0.9922</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9625</v>
+        <v>0.9482</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5248</v>
+        <v>0.517</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0325</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9625</v>
+        <v>0.9482</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9625</v>
+        <v>0.9482</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9625</v>
+        <v>0.9482</v>
       </c>
       <c r="I33" t="n">
         <v>0.9806</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9074</v>
+        <v>0.8939</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4948</v>
+        <v>0.4874</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0548</v>
+        <v>-0.0878</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9074</v>
+        <v>0.8939</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9074</v>
+        <v>0.8939</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9074</v>
+        <v>0.8939</v>
       </c>
       <c r="I34" t="n">
         <v>0.9244</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8711</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>0.475</v>
+        <v>0.4697</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.1007</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8711</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8711</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8711</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="I35" t="n">
         <v>0.8833</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8228</v>
+        <v>0.8167</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4487</v>
+        <v>0.4453</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.089</v>
+        <v>-0.1185</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8228</v>
+        <v>0.8167</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8228</v>
+        <v>0.8167</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8228</v>
+        <v>0.8167</v>
       </c>
       <c r="I36" t="n">
         <v>0.8305</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7544</v>
+        <v>0.7433</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4114</v>
+        <v>0.4053</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1166</v>
+        <v>-0.1478</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7544</v>
+        <v>0.7433</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7544</v>
+        <v>0.7433</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7544</v>
+        <v>0.7433</v>
       </c>
       <c r="I37" t="n">
         <v>0.7685999999999999</v>
@@ -2158,7 +2158,7 @@
         <v>0.394</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1294</v>
+        <v>-0.156</v>
       </c>
       <c r="E38" t="n">
         <v>0.7226</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6831</v>
+        <v>0.673</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3725</v>
+        <v>0.367</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1454</v>
+        <v>-0.1758</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6831</v>
+        <v>0.673</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6831</v>
+        <v>0.673</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6831</v>
+        <v>0.673</v>
       </c>
       <c r="I39" t="n">
         <v>0.6959</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6617</v>
+        <v>0.6519</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3608</v>
+        <v>0.3555</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1541</v>
+        <v>-0.1842</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6617</v>
+        <v>0.6519</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6617</v>
+        <v>0.6519</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6617</v>
+        <v>0.6519</v>
       </c>
       <c r="I40" t="n">
         <v>0.6741</v>
@@ -2296,7 +2296,7 @@
         <v>0.3183</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1855</v>
+        <v>-0.2113</v>
       </c>
       <c r="E41" t="n">
         <v>0.5838</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.479</v>
+        <v>0.4719</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2612</v>
+        <v>0.2573</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2279</v>
+        <v>-0.2559</v>
       </c>
       <c r="E42" t="n">
-        <v>0.479</v>
+        <v>0.4719</v>
       </c>
       <c r="F42" t="n">
-        <v>0.479</v>
+        <v>0.4719</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.479</v>
+        <v>0.4719</v>
       </c>
       <c r="I42" t="n">
         <v>0.488</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3851</v>
+        <v>0.3822</v>
       </c>
       <c r="C43" t="n">
-        <v>0.21</v>
+        <v>0.2084</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2658</v>
+        <v>-0.2916</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3851</v>
+        <v>0.3822</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3851</v>
+        <v>0.3822</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3851</v>
+        <v>0.3822</v>
       </c>
       <c r="I43" t="n">
         <v>0.3887</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.373</v>
+        <v>0.3702</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2034</v>
+        <v>0.2019</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2707</v>
+        <v>-0.2964</v>
       </c>
       <c r="E44" t="n">
-        <v>0.373</v>
+        <v>0.3702</v>
       </c>
       <c r="F44" t="n">
-        <v>0.373</v>
+        <v>0.3702</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.373</v>
+        <v>0.3702</v>
       </c>
       <c r="I44" t="n">
         <v>0.3765</v>
@@ -2470,93 +2470,93 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2641</v>
+        <v>0.2604</v>
       </c>
       <c r="C45" t="n">
-        <v>0.144</v>
+        <v>0.142</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3147</v>
+        <v>-0.3402</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2641</v>
+        <v>0.2604</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2641</v>
+        <v>0.2604</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2641</v>
+        <v>0.2604</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2691</v>
+        <v>0.2604</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2691</v>
+        <v>0.2604</v>
       </c>
       <c r="N45" t="n">
-        <v>147</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2604</v>
+        <v>0.2602</v>
       </c>
       <c r="C46" t="n">
-        <v>0.142</v>
+        <v>0.1419</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3162</v>
+        <v>-0.3402</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2604</v>
+        <v>0.2602</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2604</v>
+        <v>0.2602</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2604</v>
+        <v>0.2602</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2604</v>
+        <v>0.2691</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2604</v>
+        <v>0.2691</v>
       </c>
       <c r="N46" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47">
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2011</v>
+        <v>0.1996</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1097</v>
+        <v>0.1088</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3401</v>
+        <v>-0.3644</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2011</v>
+        <v>0.1996</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2011</v>
+        <v>0.1996</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2011</v>
+        <v>0.1996</v>
       </c>
       <c r="I47" t="n">
         <v>0.203</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1967</v>
+        <v>0.1937</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1073</v>
+        <v>0.1056</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3419</v>
+        <v>-0.3667</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1967</v>
+        <v>0.1937</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1967</v>
+        <v>0.1937</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1967</v>
+        <v>0.1937</v>
       </c>
       <c r="I48" t="n">
         <v>0.2003</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1386</v>
+        <v>0.1365</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0756</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3654</v>
+        <v>-0.3895</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1386</v>
+        <v>0.1365</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1386</v>
+        <v>0.1365</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1386</v>
+        <v>0.1365</v>
       </c>
       <c r="I49" t="n">
         <v>0.1412</v>
@@ -2710,7 +2710,7 @@
         <v>0.0707</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.369</v>
+        <v>-0.3922</v>
       </c>
       <c r="E50" t="n">
         <v>0.1297</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0357</v>
+        <v>0.0353</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0195</v>
+        <v>0.0192</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4069</v>
+        <v>-0.4298</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0357</v>
+        <v>0.0353</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0357</v>
+        <v>0.0353</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0357</v>
+        <v>0.0353</v>
       </c>
       <c r="I51" t="n">
         <v>0.0362</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0311</v>
+        <v>0.0307</v>
       </c>
       <c r="C52" t="n">
-        <v>0.017</v>
+        <v>0.0167</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4088</v>
+        <v>-0.4317</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0311</v>
+        <v>0.0307</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0311</v>
+        <v>0.0307</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0311</v>
+        <v>0.0307</v>
       </c>
       <c r="I52" t="n">
         <v>0.0315</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.019</v>
+        <v>0.0189</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0104</v>
+        <v>0.0103</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4137</v>
+        <v>-0.4364</v>
       </c>
       <c r="E53" t="n">
-        <v>0.019</v>
+        <v>0.0189</v>
       </c>
       <c r="F53" t="n">
-        <v>0.019</v>
+        <v>0.0189</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.019</v>
+        <v>0.0189</v>
       </c>
       <c r="I53" t="n">
         <v>0.0192</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1045</v>
+        <v>-0.103</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.057</v>
+        <v>-0.0562</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4636</v>
+        <v>-0.4849</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1045</v>
+        <v>-0.103</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1045</v>
+        <v>-0.103</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1045</v>
+        <v>-0.103</v>
       </c>
       <c r="I54" t="n">
         <v>-0.1065</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1089</v>
+        <v>-0.1072</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0594</v>
+        <v>-0.0585</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4654</v>
+        <v>-0.4866</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1089</v>
+        <v>-0.1072</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1089</v>
+        <v>-0.1072</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1089</v>
+        <v>-0.1072</v>
       </c>
       <c r="I55" t="n">
         <v>-0.1109</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1112</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5037</v>
+        <v>-0.5251</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2039</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3016</v>
+        <v>-0.2972</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1645</v>
+        <v>-0.1621</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5432</v>
+        <v>-0.5623</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3016</v>
+        <v>-0.2972</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3016</v>
+        <v>-0.2972</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3016</v>
+        <v>-0.2972</v>
       </c>
       <c r="I57" t="n">
         <v>-0.3073</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3671</v>
+        <v>-0.3617</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2002</v>
+        <v>-0.1972</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5697</v>
+        <v>-0.588</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3671</v>
+        <v>-0.3617</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3671</v>
+        <v>-0.3617</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3671</v>
+        <v>-0.3617</v>
       </c>
       <c r="I58" t="n">
         <v>-0.374</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2027</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5716</v>
+        <v>-0.592</v>
       </c>
       <c r="E59" t="n">
         <v>-0.3718</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3245</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.681</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5951</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6161</v>
+        <v>-0.6069</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.336</v>
+        <v>-0.3309</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6703</v>
+        <v>-0.6857</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6161</v>
+        <v>-0.6069</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.6161</v>
+        <v>-0.6069</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.6161</v>
+        <v>-0.6069</v>
       </c>
       <c r="I61" t="n">
         <v>-0.6276</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.6128</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3367</v>
+        <v>-0.3342</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6708</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.6128</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.6128</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.6128</v>
       </c>
       <c r="I62" t="n">
         <v>-0.6232</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6247</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3406</v>
+        <v>-0.3356</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6737</v>
+        <v>-0.6891</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6247</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6247</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6247</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="I63" t="n">
         <v>-0.6364</v>
@@ -3354,7 +3354,7 @@
         <v>-0.349</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.6989</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6401</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3691</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6948</v>
+        <v>-0.7135</v>
       </c>
       <c r="E65" t="n">
         <v>-0.6768</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7129</v>
+        <v>-0.7076</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3887</v>
+        <v>-0.3858</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7094</v>
+        <v>-0.7258</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7129</v>
+        <v>-0.7076</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7129</v>
+        <v>-0.7076</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7129</v>
+        <v>-0.7076</v>
       </c>
       <c r="I66" t="n">
         <v>-0.7196</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7866</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4289</v>
+        <v>-0.4257</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7391</v>
+        <v>-0.7549</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7866</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7866</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7866</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="I67" t="n">
         <v>-0.7939000000000001</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.987</v>
+        <v>-0.9796</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5382</v>
+        <v>-0.5342</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.987</v>
+        <v>-0.9796</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.987</v>
+        <v>-0.9796</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.987</v>
+        <v>-0.9796</v>
       </c>
       <c r="I68" t="n">
         <v>-0.9962</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.2774</v>
+        <v>-1.2679</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.6966</v>
+        <v>-0.6914</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9374</v>
+        <v>-0.949</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2774</v>
+        <v>-1.2679</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.2774</v>
+        <v>-1.2679</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.2774</v>
+        <v>-1.2679</v>
       </c>
       <c r="I69" t="n">
         <v>-1.2893</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.2919</v>
+        <v>-1.2823</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.7045</v>
+        <v>-0.6992</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9433</v>
+        <v>-0.9548</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2919</v>
+        <v>-1.2823</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.2919</v>
+        <v>-1.2823</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.2919</v>
+        <v>-1.2823</v>
       </c>
       <c r="I70" t="n">
         <v>-1.304</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7632</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9868</v>
+        <v>-1.0015</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3996</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.4254</v>
+        <v>-1.4042</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.7773</v>
+        <v>-0.7657</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9972</v>
+        <v>-1.0033</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.4254</v>
+        <v>-1.4042</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.4254</v>
+        <v>-1.4042</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.4254</v>
+        <v>-1.4042</v>
       </c>
       <c r="I72" t="n">
         <v>-1.4521</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.4578</v>
+        <v>-1.4469</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.789</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0103</v>
+        <v>-1.0204</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.4578</v>
+        <v>-1.4469</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.4578</v>
+        <v>-1.4469</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.4578</v>
+        <v>-1.4469</v>
       </c>
       <c r="I73" t="n">
         <v>-1.4714</v>
@@ -3814,7 +3814,7 @@
         <v>-0.9359</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1147</v>
+        <v>-1.1277</v>
       </c>
       <c r="E74" t="n">
         <v>-1.7163</v>
@@ -3860,7 +3860,7 @@
         <v>-0.999</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1614</v>
+        <v>-1.1738</v>
       </c>
       <c r="E75" t="n">
         <v>-1.832</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9997</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.162</v>
+        <v>-1.1743</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8334</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.9036</v>
+        <v>-1.8824</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.038</v>
+        <v>-1.0264</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1904</v>
+        <v>-1.1939</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.9036</v>
+        <v>-1.8824</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.9036</v>
+        <v>-1.8824</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.9036</v>
+        <v>-1.8824</v>
       </c>
       <c r="I77" t="n">
         <v>-1.9303</v>
@@ -3998,7 +3998,7 @@
         <v>-1.0541</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2023</v>
+        <v>-1.2141</v>
       </c>
       <c r="E78" t="n">
         <v>-1.9331</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.2828</v>
+        <v>-2.2489</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.2448</v>
+        <v>-1.2263</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3436</v>
+        <v>-1.3399</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.2828</v>
+        <v>-2.2489</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.2828</v>
+        <v>-2.2489</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.2828</v>
+        <v>-2.2489</v>
       </c>
       <c r="I79" t="n">
         <v>-2.3256</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.0037</v>
+        <v>-2.9813</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.6379</v>
+        <v>-1.6257</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6348</v>
+        <v>-1.6317</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.0037</v>
+        <v>-2.9813</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.0037</v>
+        <v>-2.9813</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.0037</v>
+        <v>-2.9813</v>
       </c>
       <c r="I80" t="n">
         <v>-3.0317</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.2792</v>
+        <v>-4.2157</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.3334</v>
+        <v>-2.2988</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.1501</v>
+        <v>-2.1234</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.2792</v>
+        <v>-4.2157</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.2792</v>
+        <v>-4.2157</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.2792</v>
+        <v>-4.2157</v>
       </c>
       <c r="I81" t="n">
         <v>-4.3594</v>

--- a/database/event/8249/event_8249_evp_summary.xlsx
+++ b/database/event/8249/event_8249_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.0945</v>
+        <v>3.9382</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2327</v>
+        <v>2.1475</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2104</v>
+        <v>1.1685</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0945</v>
+        <v>3.9382</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0945</v>
+        <v>3.9382</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.631</v>
+        <v>5.8946</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6161</v>
+        <v>6.5261</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6.6161</v>
+        <v>6.5261</v>
       </c>
       <c r="N2" t="n">
         <v>123</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6767</v>
+        <v>3.571</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0049</v>
+        <v>1.9472</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0218</v>
+        <v>1.0014</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6767</v>
+        <v>3.571</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6767</v>
+        <v>3.571</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7135</v>
+        <v>5.0908</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5381</v>
+        <v>5.6362</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5381</v>
+        <v>5.6362</v>
       </c>
       <c r="N3" t="n">
         <v>82</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4205</v>
+        <v>3.2658</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8652</v>
+        <v>1.7808</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9062</v>
+        <v>0.8625</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4205</v>
+        <v>3.2658</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4205</v>
+        <v>3.2658</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1509</v>
+        <v>4.4228</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8771</v>
+        <v>4.8966</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8771</v>
+        <v>4.8966</v>
       </c>
       <c r="N4" t="n">
         <v>147</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2794</v>
+        <v>3.1032</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7882</v>
+        <v>1.6921</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8425</v>
+        <v>0.7884</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2794</v>
+        <v>3.1032</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2794</v>
+        <v>3.1032</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8413</v>
+        <v>4.0669</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5133</v>
+        <v>4.5026</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5133</v>
+        <v>4.5026</v>
       </c>
       <c r="N5" t="n">
         <v>72</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2518</v>
+        <v>3.0276</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7732</v>
+        <v>1.6509</v>
       </c>
       <c r="D6" t="n">
-        <v>0.83</v>
+        <v>0.754</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2518</v>
+        <v>3.0276</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2518</v>
+        <v>3.0276</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7806</v>
+        <v>3.9016</v>
       </c>
       <c r="I6" t="n">
-        <v>4.442</v>
+        <v>4.3196</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.442</v>
+        <v>4.3196</v>
       </c>
       <c r="N6" t="n">
-        <v>157</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2205</v>
+        <v>3.0062</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7561</v>
+        <v>1.6392</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8159</v>
+        <v>0.7443</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2205</v>
+        <v>3.0062</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2205</v>
+        <v>3.0062</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.712</v>
+        <v>3.8547</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3613</v>
+        <v>4.2676</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3613</v>
+        <v>4.2676</v>
       </c>
       <c r="N7" t="n">
-        <v>81</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8">
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1469</v>
+        <v>2.9298</v>
       </c>
       <c r="C8" t="n">
-        <v>1.716</v>
+        <v>1.5976</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7827</v>
+        <v>0.7095</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1469</v>
+        <v>2.9298</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1469</v>
+        <v>2.9298</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5503</v>
+        <v>3.6876</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1714</v>
+        <v>4.0826</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1714</v>
+        <v>4.0826</v>
       </c>
       <c r="N8" t="n">
         <v>128</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0819</v>
+        <v>2.8463</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6805</v>
+        <v>1.5521</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7533</v>
+        <v>0.6715</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0819</v>
+        <v>2.8463</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0819</v>
+        <v>2.8463</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4077</v>
+        <v>3.5047</v>
       </c>
       <c r="I9" t="n">
-        <v>4.0038</v>
+        <v>3.8802</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.0038</v>
+        <v>3.8802</v>
       </c>
       <c r="N9" t="n">
         <v>129</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0317</v>
+        <v>2.8374</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6531</v>
+        <v>1.5472</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7306</v>
+        <v>0.6674</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0317</v>
+        <v>2.8374</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0317</v>
+        <v>2.8374</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2973</v>
+        <v>3.4853</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8741</v>
+        <v>3.8587</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8741</v>
+        <v>3.8587</v>
       </c>
       <c r="N10" t="n">
         <v>123</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9168</v>
+        <v>2.6863</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5905</v>
+        <v>1.4648</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6788</v>
+        <v>0.5987</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9168</v>
+        <v>2.6863</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9168</v>
+        <v>2.6863</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0451</v>
+        <v>3.1546</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5778</v>
+        <v>3.4926</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5778</v>
+        <v>3.4926</v>
       </c>
       <c r="N11" t="n">
         <v>72</v>
@@ -952,139 +952,139 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8488</v>
+        <v>2.6436</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5534</v>
+        <v>1.4415</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6481</v>
+        <v>0.5792</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8488</v>
+        <v>2.6436</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8488</v>
+        <v>2.6436</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8958</v>
+        <v>3.0611</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1389</v>
+        <v>3.389</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1389</v>
+        <v>3.389</v>
       </c>
       <c r="N12" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8327</v>
+        <v>2.6115</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5446</v>
+        <v>1.424</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6408</v>
+        <v>0.5646</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8327</v>
+        <v>2.6115</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8327</v>
+        <v>2.6115</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8603</v>
+        <v>2.9908</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3607</v>
+        <v>3.3112</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3607</v>
+        <v>3.3112</v>
       </c>
       <c r="N13" t="n">
-        <v>81</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7879</v>
+        <v>2.5568</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5202</v>
+        <v>1.3942</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6206</v>
+        <v>0.5397</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7879</v>
+        <v>2.5568</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7879</v>
+        <v>2.5568</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7879</v>
+        <v>2.871</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2756</v>
+        <v>3.0209</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2756</v>
+        <v>3.0209</v>
       </c>
       <c r="N14" t="n">
-        <v>157</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7877</v>
+        <v>2.5514</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5201</v>
+        <v>1.3912</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.5372</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7877</v>
+        <v>2.5514</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7877</v>
+        <v>2.5514</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7877</v>
+        <v>2.8592</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2754</v>
+        <v>3.1655</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2754</v>
+        <v>3.1655</v>
       </c>
       <c r="N15" t="n">
         <v>128</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6965</v>
+        <v>2.5377</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4704</v>
+        <v>1.3838</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5793</v>
+        <v>0.531</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6965</v>
+        <v>2.5377</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6965</v>
+        <v>2.5377</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6965</v>
+        <v>2.8294</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1682</v>
+        <v>3.1325</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1682</v>
+        <v>3.1325</v>
       </c>
       <c r="N16" t="n">
         <v>72</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4169</v>
+        <v>2.3995</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3179</v>
+        <v>1.3084</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4531</v>
+        <v>0.4681</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4169</v>
+        <v>2.3995</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4169</v>
+        <v>2.3995</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4169</v>
+        <v>2.5267</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8397</v>
+        <v>2.7974</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8397</v>
+        <v>2.7974</v>
       </c>
       <c r="N17" t="n">
         <v>129</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.369</v>
+        <v>2.3594</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2918</v>
+        <v>1.2866</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4315</v>
+        <v>0.4498</v>
       </c>
       <c r="E18" t="n">
-        <v>2.369</v>
+        <v>2.3594</v>
       </c>
       <c r="F18" t="n">
-        <v>2.369</v>
+        <v>2.3594</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.369</v>
+        <v>2.439</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7834</v>
+        <v>2.7003</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7834</v>
+        <v>2.7003</v>
       </c>
       <c r="N18" t="n">
         <v>181</v>
@@ -1274,231 +1274,231 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cptkurtka023</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1411</v>
+        <v>2.1365</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1675</v>
+        <v>1.165</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3286</v>
+        <v>0.3484</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1411</v>
+        <v>2.1365</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1411</v>
+        <v>2.1365</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1411</v>
+        <v>2.1365</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3208</v>
+        <v>2.306</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.3208</v>
+        <v>2.306</v>
       </c>
       <c r="N19" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1315</v>
+        <v>2.0783</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1623</v>
+        <v>1.1333</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3243</v>
+        <v>0.3219</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1315</v>
+        <v>2.0783</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1315</v>
+        <v>2.0783</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1315</v>
+        <v>2.0783</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4054</v>
+        <v>2.3009</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4054</v>
+        <v>2.3009</v>
       </c>
       <c r="N20" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0322</v>
+        <v>2.0657</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1081</v>
+        <v>1.1264</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2794</v>
+        <v>0.3161</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0322</v>
+        <v>2.0657</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0322</v>
+        <v>2.0657</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0322</v>
+        <v>2.0657</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3877</v>
+        <v>2.287</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3877</v>
+        <v>2.287</v>
       </c>
       <c r="N21" t="n">
-        <v>129</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0188</v>
+        <v>2.0646</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1008</v>
+        <v>1.1258</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2734</v>
+        <v>0.3156</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0188</v>
+        <v>2.0646</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0188</v>
+        <v>2.0646</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0188</v>
+        <v>2.0646</v>
       </c>
       <c r="I22" t="n">
-        <v>2.372</v>
+        <v>2.2858</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.372</v>
+        <v>2.2858</v>
       </c>
       <c r="N22" t="n">
-        <v>181</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>cptkurtka023</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.0175</v>
+        <v>2.0613</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1001</v>
+        <v>1.124</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2728</v>
+        <v>0.3141</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0175</v>
+        <v>2.0613</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0175</v>
+        <v>2.0613</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0175</v>
+        <v>2.0613</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3704</v>
+        <v>2.1689</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.3704</v>
+        <v>2.1689</v>
       </c>
       <c r="N23" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9907</v>
+        <v>2.0503</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0855</v>
+        <v>1.118</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2607</v>
+        <v>0.3091</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9907</v>
+        <v>2.0503</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9907</v>
+        <v>2.0503</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9907</v>
+        <v>2.0503</v>
       </c>
       <c r="I24" t="n">
-        <v>2.339</v>
+        <v>2.27</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.339</v>
+        <v>2.27</v>
       </c>
       <c r="N24" t="n">
         <v>81</v>
@@ -1550,170 +1550,170 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8516</v>
+        <v>1.8913</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0097</v>
+        <v>1.0313</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1979</v>
+        <v>0.2368</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8516</v>
+        <v>1.8913</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8516</v>
+        <v>1.8913</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8516</v>
+        <v>1.8913</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1755</v>
+        <v>2.0939</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.1755</v>
+        <v>2.0939</v>
       </c>
       <c r="N25" t="n">
-        <v>128</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.8113</v>
+        <v>1.8685</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9877</v>
+        <v>1.0189</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1797</v>
+        <v>0.2264</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8113</v>
+        <v>1.8685</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8113</v>
+        <v>1.8685</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8113</v>
+        <v>1.8685</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1282</v>
+        <v>2.0687</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.1282</v>
+        <v>2.0687</v>
       </c>
       <c r="N26" t="n">
-        <v>181</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7775</v>
+        <v>1.8613</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9692</v>
+        <v>1.0149</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1644</v>
+        <v>0.2231</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7775</v>
+        <v>1.8613</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7775</v>
+        <v>1.8613</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7775</v>
+        <v>1.8613</v>
       </c>
       <c r="I27" t="n">
-        <v>2.0885</v>
+        <v>2.0607</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.0885</v>
+        <v>2.0607</v>
       </c>
       <c r="N27" t="n">
-        <v>72</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6513</v>
+        <v>1.7726</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9004</v>
+        <v>0.9666</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1075</v>
+        <v>0.1827</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6513</v>
+        <v>1.7726</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6513</v>
+        <v>1.7726</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6513</v>
+        <v>1.7726</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9402</v>
+        <v>1.9625</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9402</v>
+        <v>1.9625</v>
       </c>
       <c r="N28" t="n">
         <v>147</v>
@@ -1734,32 +1734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.6488</v>
+        <v>1.7572</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8991</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1063</v>
+        <v>0.1757</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6488</v>
+        <v>1.7572</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6488</v>
+        <v>1.7572</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6488</v>
+        <v>1.7572</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9372</v>
+        <v>1.9455</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.9372</v>
+        <v>1.9455</v>
       </c>
       <c r="N29" t="n">
         <v>147</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4248</v>
+        <v>1.5756</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7769</v>
+        <v>0.8592</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0052</v>
+        <v>0.093</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4248</v>
+        <v>1.5756</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4248</v>
+        <v>1.5756</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4248</v>
+        <v>1.5756</v>
       </c>
       <c r="I30" t="n">
-        <v>1.674</v>
+        <v>1.7444</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.674</v>
+        <v>1.7444</v>
       </c>
       <c r="N30" t="n">
         <v>123</v>
@@ -1826,231 +1826,231 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4139</v>
+        <v>1.4933</v>
       </c>
       <c r="C31" t="n">
-        <v>0.771</v>
+        <v>0.8143</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0003</v>
+        <v>0.0556</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4139</v>
+        <v>1.4933</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4139</v>
+        <v>1.4933</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4139</v>
+        <v>1.4933</v>
       </c>
       <c r="I31" t="n">
-        <v>1.6613</v>
+        <v>1.6533</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.6613</v>
+        <v>1.6533</v>
       </c>
       <c r="N31" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.4003</v>
+        <v>1.4447</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0058</v>
+        <v>0.0335</v>
       </c>
       <c r="E32" t="n">
-        <v>1.4003</v>
+        <v>1.4447</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4003</v>
+        <v>1.4447</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4003</v>
+        <v>1.4447</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6453</v>
+        <v>1.5995</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.6453</v>
+        <v>1.5995</v>
       </c>
       <c r="N32" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>dziugss</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3362</v>
+        <v>1.3267</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7286</v>
+        <v>0.7234</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0348</v>
+        <v>-0.0203</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3362</v>
+        <v>1.3267</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3362</v>
+        <v>1.3267</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3362</v>
+        <v>1.3267</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4484</v>
+        <v>1.4688</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4484</v>
+        <v>1.4688</v>
       </c>
       <c r="N33" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>koala</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3121</v>
+        <v>1.2396</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7155</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0457</v>
+        <v>-0.0599</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3121</v>
+        <v>1.2396</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3121</v>
+        <v>1.2396</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.3121</v>
+        <v>1.2396</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3121</v>
+        <v>1.3043</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3121</v>
+        <v>1.3043</v>
       </c>
       <c r="N34" t="n">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dziugss</t>
+          <t>koala</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.3076</v>
+        <v>1.2115</v>
       </c>
       <c r="C35" t="n">
-        <v>0.713</v>
+        <v>0.6606</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0477</v>
+        <v>-0.0727</v>
       </c>
       <c r="E35" t="n">
-        <v>1.3076</v>
+        <v>1.2115</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3076</v>
+        <v>1.2115</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.3076</v>
+        <v>1.2115</v>
       </c>
       <c r="I35" t="n">
-        <v>1.5363</v>
+        <v>1.2115</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.5363</v>
+        <v>1.2115</v>
       </c>
       <c r="N35" t="n">
-        <v>147</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.208</v>
+        <v>1.1677</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6587</v>
+        <v>0.6367</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0927</v>
+        <v>-0.0926</v>
       </c>
       <c r="E36" t="n">
-        <v>1.208</v>
+        <v>1.1677</v>
       </c>
       <c r="F36" t="n">
-        <v>1.208</v>
+        <v>1.1677</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.208</v>
+        <v>1.1677</v>
       </c>
       <c r="I36" t="n">
-        <v>1.3633</v>
+        <v>1.2603</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.3633</v>
+        <v>1.2603</v>
       </c>
       <c r="N36" t="n">
         <v>143</v>
@@ -2102,185 +2102,185 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.0653</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5445</v>
+        <v>0.5809</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1872</v>
+        <v>-0.1393</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.0653</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.0653</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.0653</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0823</v>
+        <v>1.1794</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.0823</v>
+        <v>1.1794</v>
       </c>
       <c r="N37" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9671</v>
+        <v>0.9293</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5273</v>
+        <v>0.5067</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2014</v>
+        <v>-0.2012</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9671</v>
+        <v>0.9293</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9671</v>
+        <v>0.9293</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9671</v>
+        <v>0.9293</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0483</v>
+        <v>1.0288</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.0483</v>
+        <v>1.0288</v>
       </c>
       <c r="N38" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>piriajr</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9588</v>
+        <v>0.9086</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5228</v>
+        <v>0.4954</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2052</v>
+        <v>-0.2106</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9588</v>
+        <v>0.9086</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9588</v>
+        <v>0.9086</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9588</v>
+        <v>0.9086</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9588</v>
+        <v>1.0059</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9588</v>
+        <v>1.0059</v>
       </c>
       <c r="N39" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>piriajr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9411</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5132</v>
+        <v>0.4879</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2132</v>
+        <v>-0.2169</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9411</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9411</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9411</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1057</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.1057</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9347</v>
+        <v>0.8827</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5097</v>
+        <v>0.4813</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.216</v>
+        <v>-0.2224</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9347</v>
+        <v>0.8827</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9347</v>
+        <v>0.8827</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9347</v>
+        <v>0.8827</v>
       </c>
       <c r="I41" t="n">
-        <v>0.9347</v>
+        <v>0.8827</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9347</v>
+        <v>0.8827</v>
       </c>
       <c r="N41" t="n">
         <v>80</v>
@@ -2332,323 +2332,323 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8694</v>
+        <v>0.8799</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4741</v>
+        <v>0.4798</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2455</v>
+        <v>-0.2237</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8694</v>
+        <v>0.8799</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8694</v>
+        <v>0.8799</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8694</v>
+        <v>0.8799</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0215</v>
+        <v>0.9258</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.0215</v>
+        <v>0.9258</v>
       </c>
       <c r="N42" t="n">
-        <v>157</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8416</v>
+        <v>0.8693</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4589</v>
+        <v>0.474</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2581</v>
+        <v>-0.2285</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8416</v>
+        <v>0.8693</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8416</v>
+        <v>0.8693</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8416</v>
+        <v>0.8693</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9888</v>
+        <v>0.9147</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9888</v>
+        <v>0.9147</v>
       </c>
       <c r="N43" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.8198</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4576</v>
+        <v>0.447</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2592</v>
+        <v>-0.251</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.8198</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.8198</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.8198</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9097</v>
+        <v>0.9076</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9097</v>
+        <v>0.9076</v>
       </c>
       <c r="N44" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8257</v>
+        <v>0.7684</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4502</v>
+        <v>0.419</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2653</v>
+        <v>-0.2744</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8257</v>
+        <v>0.7684</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8257</v>
+        <v>0.7684</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8257</v>
+        <v>0.7684</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9701</v>
+        <v>0.8085</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.9701</v>
+        <v>0.8085</v>
       </c>
       <c r="N45" t="n">
-        <v>82</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>maxxkor</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6391</v>
+        <v>0.6283</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3485</v>
+        <v>0.3426</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3495</v>
+        <v>-0.3382</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6391</v>
+        <v>0.6283</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6391</v>
+        <v>0.6283</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6391</v>
+        <v>0.6283</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6391</v>
+        <v>0.6956</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6391</v>
+        <v>0.6956</v>
       </c>
       <c r="N46" t="n">
-        <v>89</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5658</v>
+        <v>0.6187</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3085</v>
+        <v>0.3374</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3826</v>
+        <v>-0.3426</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5658</v>
+        <v>0.6187</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5658</v>
+        <v>0.6187</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5658</v>
+        <v>0.6187</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>maxxkor</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5545</v>
+        <v>0.5536</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3024</v>
+        <v>0.3019</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3877</v>
+        <v>-0.3722</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5545</v>
+        <v>0.5536</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5545</v>
+        <v>0.5536</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5545</v>
+        <v>0.5536</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6515</v>
+        <v>0.5536</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6515</v>
+        <v>0.5536</v>
       </c>
       <c r="N48" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4494</v>
+        <v>0.4913</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2451</v>
+        <v>0.2679</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4351</v>
+        <v>-0.4006</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4494</v>
+        <v>0.4913</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4494</v>
+        <v>0.4913</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4494</v>
+        <v>0.4913</v>
       </c>
       <c r="I49" t="n">
-        <v>0.528</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.528</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="N49" t="n">
         <v>157</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3867</v>
+        <v>0.3973</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2109</v>
+        <v>0.2166</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4634</v>
+        <v>-0.4433</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3867</v>
+        <v>0.3973</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3867</v>
+        <v>0.3973</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3867</v>
+        <v>0.3973</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4364</v>
+        <v>0.4288</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4364</v>
+        <v>0.4288</v>
       </c>
       <c r="N50" t="n">
         <v>143</v>
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.306</v>
+        <v>0.2617</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1669</v>
+        <v>0.1427</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4999</v>
+        <v>-0.5051</v>
       </c>
       <c r="E51" t="n">
-        <v>0.306</v>
+        <v>0.2617</v>
       </c>
       <c r="F51" t="n">
-        <v>0.306</v>
+        <v>0.2617</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.306</v>
+        <v>0.2617</v>
       </c>
       <c r="I51" t="n">
-        <v>0.306</v>
+        <v>0.2617</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.306</v>
+        <v>0.2617</v>
       </c>
       <c r="N51" t="n">
         <v>71</v>
@@ -2792,93 +2792,93 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.2864</v>
+        <v>0.2464</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1562</v>
+        <v>0.1344</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5087</v>
+        <v>-0.512</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2864</v>
+        <v>0.2464</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2864</v>
+        <v>0.2464</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2864</v>
+        <v>0.2464</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2864</v>
+        <v>0.2659</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2864</v>
+        <v>0.2659</v>
       </c>
       <c r="N52" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.2748</v>
+        <v>0.2049</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1498</v>
+        <v>0.1117</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.514</v>
+        <v>-0.5309</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2748</v>
+        <v>0.2049</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2748</v>
+        <v>0.2049</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2748</v>
+        <v>0.2049</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3101</v>
+        <v>0.2049</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3101</v>
+        <v>0.2049</v>
       </c>
       <c r="N53" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0633</v>
+        <v>0.1058</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0345</v>
+        <v>0.0577</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.576</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0633</v>
+        <v>0.1058</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0633</v>
+        <v>0.1058</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0633</v>
+        <v>0.1058</v>
       </c>
       <c r="I54" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.1171</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.1171</v>
       </c>
       <c r="N54" t="n">
         <v>82</v>
@@ -2930,47 +2930,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0143</v>
+        <v>0.0703</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0078</v>
+        <v>0.0383</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6445</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0143</v>
+        <v>0.0703</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0143</v>
+        <v>0.0703</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0143</v>
+        <v>0.0703</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0155</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0155</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0159</v>
+        <v>0.0414</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0226</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6452</v>
+        <v>-0.6054</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0159</v>
+        <v>0.0414</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0159</v>
+        <v>0.0414</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0159</v>
+        <v>0.0414</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0187</v>
+        <v>0.0458</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0187</v>
+        <v>0.0458</v>
       </c>
       <c r="N56" t="n">
         <v>82</v>
@@ -3022,47 +3022,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.0815</v>
+        <v>-0.0352</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0444</v>
+        <v>-0.0192</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6748</v>
+        <v>-0.6402</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0815</v>
+        <v>-0.0352</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.0815</v>
+        <v>-0.0352</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.0815</v>
+        <v>-0.0352</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0958</v>
+        <v>-0.039</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.0958</v>
+        <v>-0.039</v>
       </c>
       <c r="N57" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58">
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.0828</v>
+        <v>-0.0929</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0451</v>
+        <v>-0.0507</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6754</v>
+        <v>-0.6665</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.0828</v>
+        <v>-0.0929</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.0828</v>
+        <v>-0.0929</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.0828</v>
+        <v>-0.0929</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0897</v>
+        <v>-0.0978</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.0897</v>
+        <v>-0.0978</v>
       </c>
       <c r="N58" t="n">
         <v>121</v>
@@ -3114,185 +3114,185 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dawy</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.1195</v>
+        <v>-0.1237</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0675</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.6805</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1195</v>
+        <v>-0.1237</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1195</v>
+        <v>-0.1237</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1195</v>
+        <v>-0.1237</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1295</v>
+        <v>-0.1302</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.1295</v>
+        <v>-0.1302</v>
       </c>
       <c r="N59" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Dawy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.1432</v>
+        <v>-0.1653</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0781</v>
+        <v>-0.0901</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7027</v>
+        <v>-0.6995</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.1432</v>
+        <v>-0.1653</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1432</v>
+        <v>-0.1653</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1432</v>
+        <v>-0.1653</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1683</v>
+        <v>-0.1739</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.1683</v>
+        <v>-0.1739</v>
       </c>
       <c r="N60" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>z4KR</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2821</v>
+        <v>-0.2999</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1538</v>
+        <v>-0.1635</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7654</v>
+        <v>-0.7607</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2821</v>
+        <v>-0.2999</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2821</v>
+        <v>-0.2999</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2821</v>
+        <v>-0.2999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3058</v>
+        <v>-0.2999</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3058</v>
+        <v>-0.2999</v>
       </c>
       <c r="N61" t="n">
-        <v>121</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2996</v>
+        <v>-0.3203</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1634</v>
+        <v>-0.1747</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7733</v>
+        <v>-0.77</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2996</v>
+        <v>-0.3203</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2996</v>
+        <v>-0.3203</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2996</v>
+        <v>-0.3203</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2996</v>
+        <v>-0.337</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2996</v>
+        <v>-0.337</v>
       </c>
       <c r="N62" t="n">
-        <v>80</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63">
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3224</v>
+        <v>-0.3223</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1758</v>
+        <v>-0.1757</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7836</v>
+        <v>-0.7709</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3224</v>
+        <v>-0.3223</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3224</v>
+        <v>-0.3223</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3224</v>
+        <v>-0.3223</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3788</v>
+        <v>-0.3568</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3788</v>
+        <v>-0.3568</v>
       </c>
       <c r="N63" t="n">
         <v>129</v>
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3312</v>
+        <v>-0.3521</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1806</v>
+        <v>-0.192</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7875</v>
+        <v>-0.7845</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3312</v>
+        <v>-0.3521</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3312</v>
+        <v>-0.3521</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.3312</v>
+        <v>-0.3521</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3312</v>
+        <v>-0.3521</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3312</v>
+        <v>-0.3521</v>
       </c>
       <c r="N64" t="n">
         <v>80</v>
@@ -3390,78 +3390,78 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rdnzao</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3742</v>
+        <v>-0.4007</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.204</v>
+        <v>-0.2185</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8069</v>
+        <v>-0.8066</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3742</v>
+        <v>-0.4007</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3742</v>
+        <v>-0.4007</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.3742</v>
+        <v>-0.4007</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3742</v>
+        <v>-0.4436</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.3742</v>
+        <v>-0.4436</v>
       </c>
       <c r="N65" t="n">
-        <v>89</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>doc</t>
+          <t>rdnzao</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4875</v>
+        <v>-0.4188</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2658</v>
+        <v>-0.2284</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8581</v>
+        <v>-0.8148</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4875</v>
+        <v>-0.4188</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4875</v>
+        <v>-0.4188</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4875</v>
+        <v>-0.4188</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4875</v>
+        <v>-0.4188</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4875</v>
+        <v>-0.4188</v>
       </c>
       <c r="N66" t="n">
         <v>89</v>
@@ -3482,93 +3482,93 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>doc</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5323</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3009</v>
+        <v>-0.2903</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8872</v>
+        <v>-0.8665</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5323</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5323</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5323</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.6484</v>
+        <v>-0.5323</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.6484</v>
+        <v>-0.5323</v>
       </c>
       <c r="N67" t="n">
-        <v>157</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7128</v>
+        <v>-0.7536</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3887</v>
+        <v>-0.4109</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9598</v>
+        <v>-0.9673</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7128</v>
+        <v>-0.7536</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.7128</v>
+        <v>-0.7536</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7128</v>
+        <v>-0.7536</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7726</v>
+        <v>-0.8343</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7726</v>
+        <v>-0.8343</v>
       </c>
       <c r="N68" t="n">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7411</v>
+        <v>-0.8081</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4041</v>
+        <v>-0.4406</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9726</v>
+        <v>-0.9921</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7411</v>
+        <v>-0.8081</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7411</v>
+        <v>-0.8081</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7411</v>
+        <v>-0.8081</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8033</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8033</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="N69" t="n">
         <v>121</v>
@@ -3620,47 +3620,47 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.7584</v>
+        <v>-0.8339</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4135</v>
+        <v>-0.4547</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9804</v>
+        <v>-1.0038</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.7584</v>
+        <v>-0.8339</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.7584</v>
+        <v>-0.8339</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.7584</v>
+        <v>-0.8339</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8911</v>
+        <v>-0.8774</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8911</v>
+        <v>-0.8774</v>
       </c>
       <c r="N70" t="n">
-        <v>181</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71">
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8395</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4472</v>
+        <v>-0.4578</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0082</v>
+        <v>-1.0064</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8395</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8395</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8395</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8889</v>
+        <v>-0.8833</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8889</v>
+        <v>-0.8833</v>
       </c>
       <c r="N71" t="n">
         <v>121</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9116</v>
+        <v>-0.9756</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4971</v>
+        <v>-0.532</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0496</v>
+        <v>-1.0683</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9116</v>
+        <v>-0.9756</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9116</v>
+        <v>-0.9756</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9116</v>
+        <v>-0.9756</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9881</v>
+        <v>-1.0265</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9881</v>
+        <v>-1.0265</v>
       </c>
       <c r="N72" t="n">
         <v>126</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9737</v>
+        <v>-1.0397</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5309</v>
+        <v>-0.5669</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0776</v>
+        <v>-1.0975</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9737</v>
+        <v>-1.0397</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.9737</v>
+        <v>-1.0397</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.9737</v>
+        <v>-1.0397</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.9737</v>
+        <v>-1.0397</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.9737</v>
+        <v>-1.0397</v>
       </c>
       <c r="N73" t="n">
         <v>71</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1238</v>
+        <v>-1.2145</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6128</v>
+        <v>-0.6623</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1454</v>
+        <v>-1.1771</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1238</v>
+        <v>-1.2145</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.1238</v>
+        <v>-1.2145</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.1238</v>
+        <v>-1.2145</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2682</v>
+        <v>-1.3108</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.2682</v>
+        <v>-1.3108</v>
       </c>
       <c r="N74" t="n">
         <v>143</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.2616</v>
+        <v>-1.3156</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6879</v>
+        <v>-0.7174</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2076</v>
+        <v>-1.2231</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.2616</v>
+        <v>-1.3156</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.2616</v>
+        <v>-1.3156</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.2616</v>
+        <v>-1.3156</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2616</v>
+        <v>-1.3156</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.2616</v>
+        <v>-1.3156</v>
       </c>
       <c r="N75" t="n">
         <v>71</v>
@@ -3896,93 +3896,93 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>gafolo</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3042</v>
+        <v>-1.3547</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.7387</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2268</v>
+        <v>-1.2409</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3042</v>
+        <v>-1.3547</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.3042</v>
+        <v>-1.3547</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.3042</v>
+        <v>-1.3547</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.3042</v>
+        <v>-1.3547</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.3042</v>
+        <v>-1.3547</v>
       </c>
       <c r="N76" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>gafolo</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3057</v>
+        <v>-1.3655</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.712</v>
+        <v>-0.7446</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2275</v>
+        <v>-1.2458</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3057</v>
+        <v>-1.3655</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.3057</v>
+        <v>-1.3655</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.3057</v>
+        <v>-1.3655</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.3057</v>
+        <v>-1.3655</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.3057</v>
+        <v>-1.3655</v>
       </c>
       <c r="N77" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78">
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.4495</v>
+        <v>-1.4975</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7904</v>
+        <v>-0.8166</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2924</v>
+        <v>-1.3059</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.4495</v>
+        <v>-1.4975</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.4495</v>
+        <v>-1.4975</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.4495</v>
+        <v>-1.4975</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.4495</v>
+        <v>-1.4975</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.4495</v>
+        <v>-1.4975</v>
       </c>
       <c r="N78" t="n">
         <v>80</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.5699</v>
+        <v>-1.6702</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.856</v>
+        <v>-0.9107</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3467</v>
+        <v>-1.3845</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.5699</v>
+        <v>-1.6702</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.5699</v>
+        <v>-1.6702</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.5699</v>
+        <v>-1.6702</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.8445</v>
+        <v>-1.8491</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.8445</v>
+        <v>-1.8491</v>
       </c>
       <c r="N79" t="n">
         <v>181</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.3712</v>
+        <v>-2.3805</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.293</v>
+        <v>-1.2981</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7085</v>
+        <v>-1.7079</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.3712</v>
+        <v>-2.3805</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.3712</v>
+        <v>-2.3805</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.3712</v>
+        <v>-2.3805</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.5703</v>
+        <v>-2.5048</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.5703</v>
+        <v>-2.5048</v>
       </c>
       <c r="N80" t="n">
         <v>126</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.3459</v>
+        <v>-3.2891</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.8245</v>
+        <v>-1.7935</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.1485</v>
+        <v>-2.1215</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.3459</v>
+        <v>-3.2891</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.3459</v>
+        <v>-3.2891</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.3459</v>
+        <v>-3.2891</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.9312</v>
+        <v>-3.6415</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.9312</v>
+        <v>-3.6415</v>
       </c>
       <c r="N81" t="n">
         <v>123</v>
@@ -4269,10 +4269,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0134</v>
+        <v>0.9457</v>
       </c>
       <c r="J2" t="n">
-        <v>30.402</v>
+        <v>28.371</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.19</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5856</v>
+        <v>0.5577</v>
       </c>
       <c r="J3" t="n">
-        <v>17.568</v>
+        <v>16.731</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>1.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1915</v>
+        <v>0.1964</v>
       </c>
       <c r="J4" t="n">
-        <v>5.745</v>
+        <v>5.892</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7304</v>
+        <v>-0.6827</v>
       </c>
       <c r="J5" t="n">
-        <v>-21.912</v>
+        <v>-20.481</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.74</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7808</v>
+        <v>-0.7269</v>
       </c>
       <c r="J6" t="n">
-        <v>-23.424</v>
+        <v>-21.807</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.17</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3766</v>
+        <v>0.3772</v>
       </c>
       <c r="J7" t="n">
-        <v>11.298</v>
+        <v>11.316</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3578</v>
+        <v>0.3596</v>
       </c>
       <c r="J8" t="n">
-        <v>10.734</v>
+        <v>10.788</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2412</v>
+        <v>0.2487</v>
       </c>
       <c r="J9" t="n">
-        <v>7.236</v>
+        <v>7.461</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.1008</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.712</v>
+        <v>-3.024</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.74</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3005</v>
+        <v>-0.3124</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.015000000000001</v>
+        <v>-9.372</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.29</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4496</v>
+        <v>0.4485</v>
       </c>
       <c r="J12" t="n">
-        <v>9.8912</v>
+        <v>9.867000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.09</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1671</v>
+        <v>0.178</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6762</v>
+        <v>3.916</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.07</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1353</v>
+        <v>0.1463</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9766</v>
+        <v>3.2186</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1707</v>
+        <v>-0.1832</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.7554</v>
+        <v>-4.0304</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1918</v>
+        <v>-0.2045</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.2196</v>
+        <v>-4.499</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>2.06</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1335</v>
+        <v>1.1291</v>
       </c>
       <c r="J17" t="n">
-        <v>24.937</v>
+        <v>24.8402</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.28</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3825</v>
+        <v>0.3958</v>
       </c>
       <c r="J18" t="n">
-        <v>8.414999999999999</v>
+        <v>8.707599999999999</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0353</v>
+        <v>-0.0366</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7766</v>
+        <v>-0.8052</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.72</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.333</v>
+        <v>-0.3416</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.326</v>
+        <v>-7.5152</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.333</v>
+        <v>-0.3416</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.326</v>
+        <v>-7.5152</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3034</v>
+        <v>1.2752</v>
       </c>
       <c r="J22" t="n">
-        <v>27.3714</v>
+        <v>26.7792</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0145</v>
+        <v>0.9571</v>
       </c>
       <c r="J23" t="n">
-        <v>21.3045</v>
+        <v>20.0991</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0559</v>
+        <v>0.0736</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1739</v>
+        <v>1.5456</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.93</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3053</v>
+        <v>-0.291</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.4113</v>
+        <v>-6.111</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5074</v>
+        <v>-0.4767</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.6554</v>
+        <v>-10.0107</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.46</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9159</v>
+        <v>0.8617</v>
       </c>
       <c r="J27" t="n">
-        <v>19.2339</v>
+        <v>18.0957</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.03</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1039</v>
+        <v>0.1087</v>
       </c>
       <c r="J28" t="n">
-        <v>2.1819</v>
+        <v>2.2827</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>0.93</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0946</v>
+        <v>-0.1073</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.9866</v>
+        <v>-2.2533</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1604</v>
+        <v>-0.1752</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.3684</v>
+        <v>-3.6792</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5765</v>
+        <v>-0.5775</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.1065</v>
+        <v>-12.1275</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5716</v>
+        <v>0.5484</v>
       </c>
       <c r="J32" t="n">
-        <v>12.5752</v>
+        <v>12.0648</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>0.93</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1046</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.9998</v>
+        <v>-2.3012</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>0.83</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1965</v>
+        <v>-0.2128</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.323</v>
+        <v>-4.6816</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.82</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2066</v>
+        <v>-0.2229</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.5452</v>
+        <v>-4.9038</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.66</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3618</v>
+        <v>-0.3746</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.9596</v>
+        <v>-8.241199999999999</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.81</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5131</v>
+        <v>1.5003</v>
       </c>
       <c r="J37" t="n">
-        <v>33.2882</v>
+        <v>33.0066</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.29</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7603</v>
+        <v>0.7257</v>
       </c>
       <c r="J38" t="n">
-        <v>16.7266</v>
+        <v>15.9654</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.18</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5043</v>
+        <v>0.4964</v>
       </c>
       <c r="J39" t="n">
-        <v>11.0946</v>
+        <v>10.9208</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>1.09</v>
       </c>
       <c r="I40" t="n">
-        <v>0.264</v>
+        <v>0.2769</v>
       </c>
       <c r="J40" t="n">
-        <v>5.808</v>
+        <v>6.0918</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.58</v>
+        <v>-0.5385</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.76</v>
+        <v>-11.847</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3718</v>
+        <v>0.3577</v>
       </c>
       <c r="J42" t="n">
-        <v>7.0642</v>
+        <v>6.7963</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>0.9</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.116</v>
+        <v>-0.133</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.204</v>
+        <v>-2.527</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.82</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1988</v>
+        <v>-0.2169</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.7772</v>
+        <v>-4.1211</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.71</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3049</v>
+        <v>-0.3214</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.7931</v>
+        <v>-6.1066</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.58</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4273</v>
+        <v>-0.4387</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.1187</v>
+        <v>-8.3353</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>2.26</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J47" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.23</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6103</v>
+        <v>0.5948</v>
       </c>
       <c r="J48" t="n">
-        <v>11.5957</v>
+        <v>11.3012</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.21</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5622</v>
+        <v>0.5518</v>
       </c>
       <c r="J49" t="n">
-        <v>10.6818</v>
+        <v>10.4842</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.18</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4879</v>
+        <v>0.4851</v>
       </c>
       <c r="J50" t="n">
-        <v>9.270099999999999</v>
+        <v>9.216900000000001</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.71</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9244</v>
+        <v>-0.8408</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.5636</v>
+        <v>-15.9752</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>2.28</v>
       </c>
       <c r="I52" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J52" t="n">
-        <v>29.3408</v>
+        <v>30.9952</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.52</v>
       </c>
       <c r="I53" t="n">
-        <v>1.1336</v>
+        <v>1.1023</v>
       </c>
       <c r="J53" t="n">
-        <v>18.1376</v>
+        <v>17.6368</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.28</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7176</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>11.4816</v>
+        <v>11.072</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.05</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1137</v>
+        <v>0.1425</v>
       </c>
       <c r="J55" t="n">
-        <v>1.8192</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.9807</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-15.6912</v>
+        <v>-14.2176</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>0.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0122</v>
+        <v>-0.0289</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.1952</v>
+        <v>-0.4624</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>0.84</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1696</v>
+        <v>-0.1898</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.7136</v>
+        <v>-3.0368</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2399</v>
+        <v>-0.2594</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.8384</v>
+        <v>-4.1504</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3422</v>
+        <v>-0.3592</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.4752</v>
+        <v>-5.7472</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.55</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4452</v>
+        <v>-0.4573</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.1232</v>
+        <v>-7.3168</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.86</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5361</v>
+        <v>1.5302</v>
       </c>
       <c r="J62" t="n">
-        <v>27.6498</v>
+        <v>27.5436</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.5</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1086</v>
+        <v>1.0753</v>
       </c>
       <c r="J63" t="n">
-        <v>19.9548</v>
+        <v>19.3554</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.48</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0842</v>
+        <v>1.0478</v>
       </c>
       <c r="J64" t="n">
-        <v>19.5156</v>
+        <v>18.8604</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1.07</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1756</v>
+        <v>0.2012</v>
       </c>
       <c r="J65" t="n">
-        <v>3.1608</v>
+        <v>3.6216</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3527</v>
+        <v>-0.3244</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.3486</v>
+        <v>-5.8392</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.15</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4406</v>
+        <v>0.4166</v>
       </c>
       <c r="J67" t="n">
-        <v>7.9308</v>
+        <v>7.4988</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2325</v>
+        <v>-0.2516</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.185</v>
+        <v>-4.5288</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>0.77</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2416</v>
+        <v>-0.2607</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.3488</v>
+        <v>-4.6926</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3455</v>
+        <v>-0.3618</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.219</v>
+        <v>-6.5124</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.54</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4577</v>
+        <v>-0.4686</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.2386</v>
+        <v>-8.434799999999999</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.94</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6681</v>
+        <v>1.6621</v>
       </c>
       <c r="J72" t="n">
-        <v>31.6939</v>
+        <v>31.5799</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6473</v>
+        <v>0.625</v>
       </c>
       <c r="J73" t="n">
-        <v>12.2987</v>
+        <v>11.875</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.22</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6012</v>
+        <v>0.5836</v>
       </c>
       <c r="J74" t="n">
-        <v>11.4228</v>
+        <v>11.0884</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.059</v>
+        <v>-0.0408</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.121</v>
+        <v>-0.7752</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.659</v>
+        <v>-0.6092</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.521</v>
+        <v>-11.5748</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3078</v>
+        <v>0.302</v>
       </c>
       <c r="J77" t="n">
-        <v>5.8482</v>
+        <v>5.738</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2208</v>
+        <v>0.2187</v>
       </c>
       <c r="J78" t="n">
-        <v>4.1952</v>
+        <v>4.1553</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.204</v>
+        <v>-0.2208</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.876</v>
+        <v>-4.1952</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2139</v>
+        <v>-0.2308</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.0641</v>
+        <v>-4.3852</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4427</v>
+        <v>-0.4524</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.411300000000001</v>
+        <v>-8.595599999999999</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.47</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1082</v>
+        <v>1.0672</v>
       </c>
       <c r="J82" t="n">
-        <v>25.4886</v>
+        <v>24.5456</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.39</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9942</v>
+        <v>0.9356</v>
       </c>
       <c r="J83" t="n">
-        <v>22.8666</v>
+        <v>21.5188</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1577</v>
+        <v>0.1733</v>
       </c>
       <c r="J84" t="n">
-        <v>3.6271</v>
+        <v>3.9859</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0118</v>
+        <v>0.0301</v>
       </c>
       <c r="J85" t="n">
-        <v>0.2714</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1764</v>
+        <v>-0.1676</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.0572</v>
+        <v>-3.8548</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.12</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3633</v>
+        <v>0.3473</v>
       </c>
       <c r="J87" t="n">
-        <v>8.3559</v>
+        <v>7.9879</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2046</v>
+        <v>0.1955</v>
       </c>
       <c r="J88" t="n">
-        <v>4.7058</v>
+        <v>4.4965</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2066</v>
+        <v>-0.2252</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.7518</v>
+        <v>-5.1796</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.62</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3866</v>
+        <v>-0.4005</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.8918</v>
+        <v>-9.211499999999999</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.42</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5712</v>
+        <v>-0.5745</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.1376</v>
+        <v>-13.2135</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.18</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4672</v>
+        <v>0.4475</v>
       </c>
       <c r="J92" t="n">
-        <v>8.876799999999999</v>
+        <v>8.5025</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.05</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1884</v>
+        <v>0.1836</v>
       </c>
       <c r="J93" t="n">
-        <v>3.5796</v>
+        <v>3.4884</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1999</v>
+        <v>-0.2178</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.7981</v>
+        <v>-4.1382</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.59</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4196</v>
+        <v>-0.4312</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.9724</v>
+        <v>-8.1928</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4474</v>
+        <v>-0.4575</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.5006</v>
+        <v>-8.692500000000001</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.96</v>
       </c>
       <c r="I97" t="n">
-        <v>1.6917</v>
+        <v>1.6867</v>
       </c>
       <c r="J97" t="n">
-        <v>32.1423</v>
+        <v>32.0473</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7603</v>
+        <v>0.7257</v>
       </c>
       <c r="J98" t="n">
-        <v>14.4457</v>
+        <v>13.7883</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>1.27</v>
       </c>
       <c r="I99" t="n">
-        <v>0.715</v>
+        <v>0.6855</v>
       </c>
       <c r="J99" t="n">
-        <v>13.585</v>
+        <v>13.0245</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.85</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5532</v>
+        <v>-0.5143</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.5108</v>
+        <v>-9.771699999999999</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.84</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.58</v>
+        <v>-0.5385</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.02</v>
+        <v>-10.2315</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3</v>
+        <v>0.3129</v>
       </c>
       <c r="J102" t="n">
-        <v>6.9</v>
+        <v>7.1967</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.12</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1942</v>
+        <v>0.2087</v>
       </c>
       <c r="J103" t="n">
-        <v>4.4666</v>
+        <v>4.8001</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1663</v>
+        <v>0.1808</v>
       </c>
       <c r="J104" t="n">
-        <v>3.8249</v>
+        <v>4.1584</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.093</v>
+        <v>0.1053</v>
       </c>
       <c r="J105" t="n">
-        <v>2.139</v>
+        <v>2.4219</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2154</v>
+        <v>-0.2275</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.9542</v>
+        <v>-5.2325</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.68</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9427</v>
+        <v>0.8983</v>
       </c>
       <c r="J107" t="n">
-        <v>21.6821</v>
+        <v>20.6609</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0279</v>
+        <v>0.0333</v>
       </c>
       <c r="J108" t="n">
-        <v>0.6417</v>
+        <v>0.7659</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.0161</v>
+        <v>-0.0115</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.89</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1466</v>
+        <v>-0.1593</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.3718</v>
+        <v>-3.6639</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.48</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5382</v>
+        <v>-0.5405</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.3786</v>
+        <v>-12.4315</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>0.464</v>
+        <v>0.4523</v>
       </c>
       <c r="J112" t="n">
-        <v>8.816000000000001</v>
+        <v>8.5937</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2456</v>
+        <v>0.247</v>
       </c>
       <c r="J113" t="n">
-        <v>4.6664</v>
+        <v>4.693</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.06</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1797</v>
+        <v>0.1831</v>
       </c>
       <c r="J114" t="n">
-        <v>3.4143</v>
+        <v>3.4789</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.88</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1483</v>
+        <v>-0.1632</v>
       </c>
       <c r="J115" t="n">
-        <v>-2.8177</v>
+        <v>-3.1008</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.42</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5841</v>
+        <v>-0.5848</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.0979</v>
+        <v>-11.1112</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>2.03</v>
       </c>
       <c r="I117" t="n">
-        <v>1.7448</v>
+        <v>1.7461</v>
       </c>
       <c r="J117" t="n">
-        <v>33.1512</v>
+        <v>33.1759</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.4302</v>
+        <v>1.4168</v>
       </c>
       <c r="J118" t="n">
-        <v>27.1738</v>
+        <v>26.9192</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.44</v>
       </c>
       <c r="I119" t="n">
-        <v>1.0398</v>
+        <v>0.9938</v>
       </c>
       <c r="J119" t="n">
-        <v>19.7562</v>
+        <v>18.8822</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.72</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.9014</v>
+        <v>-0.8205</v>
       </c>
       <c r="J120" t="n">
-        <v>-17.1266</v>
+        <v>-15.5895</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.021</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.399</v>
+        <v>-17.5731</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.34</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5242</v>
       </c>
       <c r="J122" t="n">
-        <v>12.3004</v>
+        <v>12.0566</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3576</v>
+        <v>0.3589</v>
       </c>
       <c r="J123" t="n">
-        <v>8.2248</v>
+        <v>8.2547</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0852</v>
+        <v>-0.0968</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.9596</v>
+        <v>-2.2264</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.78</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2554</v>
+        <v>-0.2693</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.8742</v>
+        <v>-6.1939</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.58</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4443</v>
+        <v>-0.4522</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.2189</v>
+        <v>-10.4006</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.8</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9559</v>
+        <v>0.9313</v>
       </c>
       <c r="J127" t="n">
-        <v>21.9857</v>
+        <v>21.4199</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.41</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5347</v>
+        <v>0.54</v>
       </c>
       <c r="J128" t="n">
-        <v>12.2981</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1296</v>
+        <v>0.1457</v>
       </c>
       <c r="J129" t="n">
-        <v>2.9808</v>
+        <v>3.3511</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3227</v>
+        <v>-0.3317</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.4221</v>
+        <v>-7.6291</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.71</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3417</v>
+        <v>-0.3502</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.8591</v>
+        <v>-8.054600000000001</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.76</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4044</v>
+        <v>1.3941</v>
       </c>
       <c r="J132" t="n">
-        <v>22.4704</v>
+        <v>22.3056</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.71</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3465</v>
+        <v>1.3327</v>
       </c>
       <c r="J133" t="n">
-        <v>21.544</v>
+        <v>21.3232</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.45</v>
       </c>
       <c r="I134" t="n">
-        <v>1.0384</v>
+        <v>0.9959</v>
       </c>
       <c r="J134" t="n">
-        <v>16.6144</v>
+        <v>15.9344</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>1.33</v>
       </c>
       <c r="I135" t="n">
-        <v>0.8153</v>
+        <v>0.781</v>
       </c>
       <c r="J135" t="n">
-        <v>13.0448</v>
+        <v>12.496</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3042</v>
+        <v>-0.2751</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.8672</v>
+        <v>-4.4016</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.27</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7153</v>
+        <v>0.6612</v>
       </c>
       <c r="J137" t="n">
-        <v>11.4448</v>
+        <v>10.5792</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>0.77</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2371</v>
+        <v>-0.2573</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.7936</v>
+        <v>-4.1168</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4324</v>
+        <v>-0.4458</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.9184</v>
+        <v>-7.1328</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.55</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4418</v>
+        <v>-0.4546</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.0688</v>
+        <v>-7.2736</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.53</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4604</v>
+        <v>-0.4722</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.3664</v>
+        <v>-7.5552</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.49</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1472</v>
+        <v>1.1069</v>
       </c>
       <c r="J142" t="n">
-        <v>22.944</v>
+        <v>22.138</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.16</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4742</v>
+        <v>0.4646</v>
       </c>
       <c r="J143" t="n">
-        <v>9.484</v>
+        <v>9.292</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2316</v>
+        <v>0.2402</v>
       </c>
       <c r="J144" t="n">
-        <v>4.632</v>
+        <v>4.804</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.97</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1639</v>
+        <v>-0.1589</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.278</v>
+        <v>-3.178</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1989</v>
+        <v>-0.1927</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.978</v>
+        <v>-3.854</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.94</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3581</v>
+        <v>1.3511</v>
       </c>
       <c r="J147" t="n">
-        <v>27.162</v>
+        <v>27.022</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>0.97</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0553</v>
+        <v>-0.0622</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.106</v>
+        <v>-1.244</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2351</v>
+        <v>-0.2472</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.702</v>
+        <v>-4.944</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.265</v>
+        <v>-0.2768</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.3</v>
+        <v>-5.536</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2748</v>
+        <v>-0.2865</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.496</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.26</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6824</v>
+        <v>0.6337</v>
       </c>
       <c r="J152" t="n">
-        <v>11.6008</v>
+        <v>10.7729</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.71</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2944</v>
+        <v>-0.3132</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.0048</v>
+        <v>-5.3244</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.66</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3413</v>
+        <v>-0.3585</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.8021</v>
+        <v>-6.0945</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.63</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3694</v>
+        <v>-0.3855</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.2798</v>
+        <v>-6.5535</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4907</v>
+        <v>-0.5003</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.341900000000001</v>
+        <v>-8.505100000000001</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>2.04</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7116</v>
+        <v>1.7183</v>
       </c>
       <c r="J157" t="n">
-        <v>29.0972</v>
+        <v>29.2111</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.67</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2932</v>
+        <v>1.2772</v>
       </c>
       <c r="J158" t="n">
-        <v>21.9844</v>
+        <v>21.7124</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.61</v>
       </c>
       <c r="I159" t="n">
-        <v>1.2236</v>
+        <v>1.2026</v>
       </c>
       <c r="J159" t="n">
-        <v>20.8012</v>
+        <v>20.4442</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.45</v>
       </c>
       <c r="I160" t="n">
-        <v>1.0353</v>
+        <v>0.9931</v>
       </c>
       <c r="J160" t="n">
-        <v>17.6001</v>
+        <v>16.8827</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.64</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.1161</v>
+        <v>-1.0036</v>
       </c>
       <c r="J161" t="n">
-        <v>-18.9737</v>
+        <v>-17.0612</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.0509</v>
+        <v>-0.0702</v>
       </c>
       <c r="J162" t="n">
-        <v>-0.9162</v>
+        <v>-1.2636</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>0.76</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2481</v>
+        <v>-0.2678</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.4658</v>
+        <v>-4.8204</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>0.75</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2572</v>
+        <v>-0.2769</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.6296</v>
+        <v>-4.9842</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.68</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3219</v>
+        <v>-0.34</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.7942</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.61</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3876</v>
+        <v>-0.4029</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.9768</v>
+        <v>-7.2522</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>1.56</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1854</v>
+        <v>1.1574</v>
       </c>
       <c r="J167" t="n">
-        <v>21.3372</v>
+        <v>20.8332</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>1.5</v>
       </c>
       <c r="I168" t="n">
-        <v>1.112</v>
+        <v>1.0783</v>
       </c>
       <c r="J168" t="n">
-        <v>20.016</v>
+        <v>19.4094</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>1.3</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7662</v>
+        <v>0.7343</v>
       </c>
       <c r="J169" t="n">
-        <v>13.7916</v>
+        <v>13.2174</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>1.3</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7662</v>
+        <v>0.7343</v>
       </c>
       <c r="J170" t="n">
-        <v>13.7916</v>
+        <v>13.2174</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>1.07</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1805</v>
+        <v>0.2047</v>
       </c>
       <c r="J171" t="n">
-        <v>3.249</v>
+        <v>3.6846</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>2.49</v>
       </c>
       <c r="I172" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J172" t="n">
-        <v>27.507</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.84</v>
       </c>
       <c r="I173" t="n">
-        <v>1.4777</v>
+        <v>1.4747</v>
       </c>
       <c r="J173" t="n">
-        <v>22.1655</v>
+        <v>22.1205</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>1.38</v>
       </c>
       <c r="I174" t="n">
-        <v>0.906</v>
+        <v>0.8641</v>
       </c>
       <c r="J174" t="n">
-        <v>13.59</v>
+        <v>12.9615</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>1.25</v>
       </c>
       <c r="I175" t="n">
-        <v>0.613</v>
+        <v>0.6059</v>
       </c>
       <c r="J175" t="n">
-        <v>9.195</v>
+        <v>9.0885</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.72</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.9367</v>
+        <v>-0.8455</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.0505</v>
+        <v>-12.6825</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.17</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4995</v>
+        <v>0.4678</v>
       </c>
       <c r="J177" t="n">
-        <v>7.4925</v>
+        <v>7.017</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>0.77</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2394</v>
+        <v>-0.2591</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.591</v>
+        <v>-3.8865</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>0.76</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2487</v>
+        <v>-0.2683</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.7305</v>
+        <v>-4.0245</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.61</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3885</v>
+        <v>-0.4036</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.8275</v>
+        <v>-6.054</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.46</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5281</v>
+        <v>-0.5352</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.9215</v>
+        <v>-8.028</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.86</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5665</v>
+        <v>1.5571</v>
       </c>
       <c r="J182" t="n">
-        <v>29.7635</v>
+        <v>29.5849</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.56</v>
       </c>
       <c r="I183" t="n">
-        <v>1.2025</v>
+        <v>1.1724</v>
       </c>
       <c r="J183" t="n">
-        <v>22.8475</v>
+        <v>22.2756</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.31</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8011</v>
+        <v>0.7625</v>
       </c>
       <c r="J184" t="n">
-        <v>15.2209</v>
+        <v>14.4875</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0638</v>
+        <v>-0.0442</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.2122</v>
+        <v>-0.8398</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.58</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.219</v>
+        <v>-1.0979</v>
       </c>
       <c r="J186" t="n">
-        <v>-23.161</v>
+        <v>-20.8601</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.07</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2279</v>
+        <v>0.2239</v>
       </c>
       <c r="J187" t="n">
-        <v>4.3301</v>
+        <v>4.2541</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0735</v>
+        <v>-0.0878</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.3965</v>
+        <v>-1.6682</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.9</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1202</v>
+        <v>-0.1363</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.2838</v>
+        <v>-2.5897</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1721</v>
+        <v>-0.1892</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.2699</v>
+        <v>-3.5948</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.53</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4773</v>
+        <v>-0.4854</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.0687</v>
+        <v>-9.2226</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.4</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7997</v>
+        <v>0.7601</v>
       </c>
       <c r="J192" t="n">
-        <v>23.1913</v>
+        <v>22.0429</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0856</v>
+        <v>-0.097</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.4824</v>
+        <v>-2.813</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.89</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1424</v>
+        <v>-0.156</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.1296</v>
+        <v>-4.524</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.84</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1953</v>
+        <v>-0.2095</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.6637</v>
+        <v>-6.0755</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.8</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.236</v>
+        <v>-0.25</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.844</v>
+        <v>-7.25</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.86</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6309</v>
+        <v>1.6146</v>
       </c>
       <c r="J197" t="n">
-        <v>47.2961</v>
+        <v>46.8234</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.07</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2391</v>
+        <v>0.2453</v>
       </c>
       <c r="J198" t="n">
-        <v>6.9339</v>
+        <v>7.1137</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>0.88</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4333</v>
+        <v>-0.4132</v>
       </c>
       <c r="J199" t="n">
-        <v>-12.5657</v>
+        <v>-11.9828</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4612</v>
+        <v>-0.4386</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.3748</v>
+        <v>-12.7194</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.8</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.6068</v>
       </c>
       <c r="J201" t="n">
-        <v>-18.8123</v>
+        <v>-17.5972</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.31</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7097</v>
+        <v>0.6688</v>
       </c>
       <c r="J202" t="n">
-        <v>12.7746</v>
+        <v>12.0384</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>0.99</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0012</v>
+        <v>-0.0103</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.0216</v>
+        <v>-0.1854</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2205</v>
+        <v>-0.238</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.969</v>
+        <v>-4.284</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.7</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3172</v>
+        <v>-0.3328</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.7096</v>
+        <v>-5.9904</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.44</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5615</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.044</v>
+        <v>-10.107</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.89</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5772</v>
+        <v>1.5723</v>
       </c>
       <c r="J207" t="n">
-        <v>28.3896</v>
+        <v>28.3014</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1247</v>
+        <v>1.092</v>
       </c>
       <c r="J208" t="n">
-        <v>20.2446</v>
+        <v>19.656</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1.41</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9908</v>
+        <v>0.9401</v>
       </c>
       <c r="J209" t="n">
-        <v>17.8344</v>
+        <v>16.9218</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>1.25</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6522</v>
+        <v>0.6332</v>
       </c>
       <c r="J210" t="n">
-        <v>11.7396</v>
+        <v>11.3976</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.66</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.0481</v>
+        <v>-0.9479</v>
       </c>
       <c r="J211" t="n">
-        <v>-18.8658</v>
+        <v>-17.0622</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.5</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1701</v>
+        <v>1.1296</v>
       </c>
       <c r="J212" t="n">
-        <v>25.7422</v>
+        <v>24.8512</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.27</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7559</v>
+        <v>0.7138</v>
       </c>
       <c r="J213" t="n">
-        <v>16.6298</v>
+        <v>15.7036</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>1.15</v>
       </c>
       <c r="I214" t="n">
-        <v>0.456</v>
+        <v>0.4464</v>
       </c>
       <c r="J214" t="n">
-        <v>10.032</v>
+        <v>9.8208</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.89</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4055</v>
+        <v>-0.3877</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.920999999999999</v>
+        <v>-8.529400000000001</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.68</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.8702</v>
       </c>
       <c r="J216" t="n">
-        <v>-20.8802</v>
+        <v>-19.1444</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.29</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5889</v>
+        <v>0.5736</v>
       </c>
       <c r="J217" t="n">
-        <v>12.9558</v>
+        <v>12.6192</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.17</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3744</v>
+        <v>0.3756</v>
       </c>
       <c r="J218" t="n">
-        <v>8.236800000000001</v>
+        <v>8.263199999999999</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.15</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3369</v>
+        <v>0.3403</v>
       </c>
       <c r="J219" t="n">
-        <v>7.4118</v>
+        <v>7.4866</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1376</v>
+        <v>-0.1495</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.0272</v>
+        <v>-3.289</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.64</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3956</v>
+        <v>-0.4044</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.703200000000001</v>
+        <v>-8.896800000000001</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.41</v>
       </c>
       <c r="I222" t="n">
-        <v>1.043</v>
+        <v>0.9873</v>
       </c>
       <c r="J222" t="n">
-        <v>25.032</v>
+        <v>23.6952</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.5522</v>
+        <v>0.5345</v>
       </c>
       <c r="J223" t="n">
-        <v>13.2528</v>
+        <v>12.828</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>1.16</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4764</v>
+        <v>0.4661</v>
       </c>
       <c r="J224" t="n">
-        <v>11.4336</v>
+        <v>11.1864</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2931</v>
+        <v>-0.2825</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.0344</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.91</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3534</v>
+        <v>-0.3386</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.4816</v>
+        <v>-8.1264</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4965</v>
+        <v>0.4832</v>
       </c>
       <c r="J227" t="n">
-        <v>11.916</v>
+        <v>11.5968</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.15</v>
       </c>
       <c r="I228" t="n">
-        <v>0.3635</v>
+        <v>0.3598</v>
       </c>
       <c r="J228" t="n">
-        <v>8.724</v>
+        <v>8.635199999999999</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.07</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1985</v>
+        <v>0.2024</v>
       </c>
       <c r="J229" t="n">
-        <v>4.764</v>
+        <v>4.8576</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.64</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3859</v>
+        <v>-0.3968</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.2616</v>
+        <v>-9.523199999999999</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.63</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3952</v>
+        <v>-0.4057</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.4848</v>
+        <v>-9.736800000000001</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4745</v>
+        <v>0.4455</v>
       </c>
       <c r="J232" t="n">
-        <v>9.015499999999999</v>
+        <v>8.464499999999999</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.91</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1109</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.7347</v>
+        <v>-2.1071</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.89</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1148</v>
+        <v>-0.1348</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.1812</v>
+        <v>-2.5612</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.49</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5012</v>
+        <v>-0.5099</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.5228</v>
+        <v>-9.6881</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.35</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.63</v>
+        <v>-0.6299</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.97</v>
+        <v>-11.9681</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.69</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3525</v>
+        <v>1.3337</v>
       </c>
       <c r="J237" t="n">
-        <v>25.6975</v>
+        <v>25.3403</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.26</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6597</v>
       </c>
       <c r="J238" t="n">
-        <v>12.996</v>
+        <v>12.5343</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.25</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6609</v>
+        <v>0.6392</v>
       </c>
       <c r="J239" t="n">
-        <v>12.5571</v>
+        <v>12.1448</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.16</v>
       </c>
       <c r="I240" t="n">
-        <v>0.441</v>
+        <v>0.4419</v>
       </c>
       <c r="J240" t="n">
-        <v>8.379</v>
+        <v>8.396100000000001</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.14</v>
       </c>
       <c r="I241" t="n">
-        <v>0.3887</v>
+        <v>0.3944</v>
       </c>
       <c r="J241" t="n">
-        <v>7.3853</v>
+        <v>7.4936</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.16</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3977</v>
+        <v>0.3888</v>
       </c>
       <c r="J242" t="n">
-        <v>8.7494</v>
+        <v>8.553599999999999</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.11</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2967</v>
+        <v>0.2939</v>
       </c>
       <c r="J243" t="n">
-        <v>6.5274</v>
+        <v>6.4658</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.03</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1152</v>
+        <v>0.1169</v>
       </c>
       <c r="J244" t="n">
-        <v>2.5344</v>
+        <v>2.5718</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3342</v>
+        <v>-0.3478</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.3524</v>
+        <v>-7.6516</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.53</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4827</v>
+        <v>-0.4897</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.6194</v>
+        <v>-10.7734</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.69</v>
       </c>
       <c r="I247" t="n">
-        <v>1.3853</v>
+        <v>1.3628</v>
       </c>
       <c r="J247" t="n">
-        <v>30.4766</v>
+        <v>29.9816</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.33</v>
       </c>
       <c r="I248" t="n">
-        <v>0.8672</v>
+        <v>0.8166</v>
       </c>
       <c r="J248" t="n">
-        <v>19.0784</v>
+        <v>17.9652</v>
       </c>
     </row>
     <row r="249">
@@ -14189,10 +14189,10 @@
         <v>0.97</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.178</v>
+        <v>-0.1687</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.916</v>
+        <v>-3.7114</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.8</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6713</v>
+        <v>-0.6227</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.7686</v>
+        <v>-13.6994</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.64</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3003</v>
+        <v>1.2768</v>
       </c>
       <c r="J252" t="n">
-        <v>26.006</v>
+        <v>25.536</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.43</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0363</v>
+        <v>0.9873</v>
       </c>
       <c r="J253" t="n">
-        <v>20.726</v>
+        <v>19.746</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.34</v>
       </c>
       <c r="I254" t="n">
-        <v>0.867</v>
+        <v>0.8206</v>
       </c>
       <c r="J254" t="n">
-        <v>17.34</v>
+        <v>16.412</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>1.03</v>
       </c>
       <c r="I255" t="n">
-        <v>0.0683</v>
+        <v>0.0929</v>
       </c>
       <c r="J255" t="n">
-        <v>1.366</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.89</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4481</v>
+        <v>-0.4176</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.962</v>
+        <v>-8.352</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.17</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4382</v>
+        <v>0.4224</v>
       </c>
       <c r="J257" t="n">
-        <v>8.763999999999999</v>
+        <v>8.448</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>0.98</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0193</v>
+        <v>-0.0299</v>
       </c>
       <c r="J258" t="n">
-        <v>-0.386</v>
+        <v>-0.598</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.93</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0857</v>
+        <v>-0.1006</v>
       </c>
       <c r="J259" t="n">
-        <v>-1.714</v>
+        <v>-2.012</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.74</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2802</v>
+        <v>-0.2965</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.604</v>
+        <v>-5.93</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.47</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5319</v>
+        <v>-0.5369</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.638</v>
+        <v>-10.738</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.74</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4366</v>
+        <v>1.4185</v>
       </c>
       <c r="J262" t="n">
-        <v>40.2248</v>
+        <v>39.718</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.38</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9649</v>
+        <v>0.9077</v>
       </c>
       <c r="J263" t="n">
-        <v>27.0172</v>
+        <v>25.4156</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.24</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6509</v>
+        <v>0.6274</v>
       </c>
       <c r="J264" t="n">
-        <v>18.2252</v>
+        <v>17.5672</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>0.9</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4074</v>
+        <v>-0.3829</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.4072</v>
+        <v>-10.7212</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.82</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6269</v>
+        <v>-0.5816</v>
       </c>
       <c r="J266" t="n">
-        <v>-17.5532</v>
+        <v>-16.2848</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.18</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4428</v>
+        <v>0.4295</v>
       </c>
       <c r="J267" t="n">
-        <v>12.3984</v>
+        <v>12.026</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.95</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.8368</v>
+        <v>-2.1896</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.9</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1237</v>
+        <v>-0.1389</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.4636</v>
+        <v>-3.8892</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.72</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3037</v>
+        <v>-0.3186</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.5036</v>
+        <v>-8.9208</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.7</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3229</v>
+        <v>-0.3372</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.0412</v>
+        <v>-9.441599999999999</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>2.03</v>
       </c>
       <c r="I272" t="n">
-        <v>1.7322</v>
+        <v>1.7349</v>
       </c>
       <c r="J272" t="n">
-        <v>29.4474</v>
+        <v>29.4933</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.69</v>
       </c>
       <c r="I273" t="n">
-        <v>1.3379</v>
+        <v>1.3208</v>
       </c>
       <c r="J273" t="n">
-        <v>22.7443</v>
+        <v>22.4536</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.18</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4778</v>
+        <v>0.4781</v>
       </c>
       <c r="J274" t="n">
-        <v>8.1226</v>
+        <v>8.127700000000001</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>1.05</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1137</v>
+        <v>0.1425</v>
       </c>
       <c r="J275" t="n">
-        <v>1.9329</v>
+        <v>2.4225</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.87</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5253</v>
+        <v>-0.4837</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.930099999999999</v>
+        <v>-8.222899999999999</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.12</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3449</v>
+        <v>0.3337</v>
       </c>
       <c r="J277" t="n">
-        <v>5.8633</v>
+        <v>5.6729</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0405</v>
+        <v>0.0293</v>
       </c>
       <c r="J278" t="n">
-        <v>0.6885</v>
+        <v>0.4981</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.73</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2874</v>
+        <v>-0.3041</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.8858</v>
+        <v>-5.1697</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.68</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3352</v>
+        <v>-0.3503</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.6984</v>
+        <v>-5.9551</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3446</v>
+        <v>-0.3594</v>
       </c>
       <c r="J281" t="n">
-        <v>-5.8582</v>
+        <v>-6.1098</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.68</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9231</v>
+        <v>0.8824</v>
       </c>
       <c r="J282" t="n">
-        <v>21.2313</v>
+        <v>20.2952</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.37</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5457</v>
+        <v>0.539</v>
       </c>
       <c r="J283" t="n">
-        <v>12.5511</v>
+        <v>12.397</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.9</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1411</v>
+        <v>-0.1523</v>
       </c>
       <c r="J284" t="n">
-        <v>-3.2453</v>
+        <v>-3.5029</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3523</v>
+        <v>-0.3621</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.1029</v>
+        <v>-8.3283</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.67</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.371</v>
+        <v>-0.3802</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.532999999999999</v>
+        <v>-8.7446</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.5</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6334</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J287" t="n">
-        <v>14.5682</v>
+        <v>14.5498</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.21</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2979</v>
+        <v>0.314</v>
       </c>
       <c r="J288" t="n">
-        <v>6.8517</v>
+        <v>7.222</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.19</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2733</v>
+        <v>0.2899</v>
       </c>
       <c r="J289" t="n">
-        <v>6.2859</v>
+        <v>6.6677</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.95</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.092</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.116</v>
+        <v>-2.2678</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.93</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1165</v>
+        <v>-0.1243</v>
       </c>
       <c r="J291" t="n">
-        <v>-2.6795</v>
+        <v>-2.8589</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.67</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3444</v>
+        <v>1.3223</v>
       </c>
       <c r="J292" t="n">
-        <v>29.5768</v>
+        <v>29.0906</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.58</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2331</v>
+        <v>1.2041</v>
       </c>
       <c r="J293" t="n">
-        <v>27.1282</v>
+        <v>26.4902</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.33</v>
       </c>
       <c r="I294" t="n">
-        <v>0.8516</v>
+        <v>0.8058</v>
       </c>
       <c r="J294" t="n">
-        <v>18.7352</v>
+        <v>17.7276</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>1.07</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2057</v>
+        <v>0.2223</v>
       </c>
       <c r="J295" t="n">
-        <v>4.5254</v>
+        <v>4.8906</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.54</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.306</v>
+        <v>-1.173</v>
       </c>
       <c r="J296" t="n">
-        <v>-28.732</v>
+        <v>-25.806</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.09</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2364</v>
+        <v>0.2403</v>
       </c>
       <c r="J297" t="n">
-        <v>5.2008</v>
+        <v>5.2866</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.04</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1248</v>
+        <v>0.1309</v>
       </c>
       <c r="J298" t="n">
-        <v>2.7456</v>
+        <v>2.8798</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.93</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.096</v>
+        <v>-0.1084</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.112</v>
+        <v>-2.3848</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.91</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1188</v>
+        <v>-0.1321</v>
       </c>
       <c r="J300" t="n">
-        <v>-2.6136</v>
+        <v>-2.9062</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.83</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2039</v>
+        <v>-0.2185</v>
       </c>
       <c r="J301" t="n">
-        <v>-4.4858</v>
+        <v>-4.807</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.6</v>
       </c>
       <c r="I302" t="n">
-        <v>1.287</v>
+        <v>1.2562</v>
       </c>
       <c r="J302" t="n">
-        <v>29.601</v>
+        <v>28.8926</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>1.34</v>
       </c>
       <c r="I303" t="n">
-        <v>0.906</v>
+        <v>0.8479</v>
       </c>
       <c r="J303" t="n">
-        <v>20.838</v>
+        <v>19.5017</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>1.15</v>
       </c>
       <c r="I304" t="n">
-        <v>0.4474</v>
+        <v>0.4405</v>
       </c>
       <c r="J304" t="n">
-        <v>10.2902</v>
+        <v>10.1315</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.91</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3582</v>
+        <v>-0.3419</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.2386</v>
+        <v>-7.8637</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.9346</v>
+        <v>-0.856</v>
       </c>
       <c r="J306" t="n">
-        <v>-21.4958</v>
+        <v>-19.688</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.01</v>
       </c>
       <c r="I307" t="n">
-        <v>0.0508</v>
+        <v>0.0527</v>
       </c>
       <c r="J307" t="n">
-        <v>1.1684</v>
+        <v>1.2121</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>0.99</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0147</v>
+        <v>-0.0208</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.3381</v>
+        <v>-0.4784</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>0.97</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0448</v>
+        <v>-0.0542</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.0304</v>
+        <v>-1.2466</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.92</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1051</v>
+        <v>-0.1186</v>
       </c>
       <c r="J310" t="n">
-        <v>-2.4173</v>
+        <v>-2.7278</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.78</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.251</v>
+        <v>-0.2659</v>
       </c>
       <c r="J311" t="n">
-        <v>-5.773</v>
+        <v>-6.1157</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.33</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8394</v>
       </c>
       <c r="J312" t="n">
-        <v>21.5928</v>
+        <v>20.1456</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.15</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4565</v>
+        <v>0.4467</v>
       </c>
       <c r="J313" t="n">
-        <v>10.956</v>
+        <v>10.7208</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.04</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1449</v>
+        <v>0.1556</v>
       </c>
       <c r="J314" t="n">
-        <v>3.4776</v>
+        <v>3.7344</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1449</v>
+        <v>0.1556</v>
       </c>
       <c r="J315" t="n">
-        <v>3.4776</v>
+        <v>3.7344</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.92</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.317</v>
+        <v>-0.3064</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.608</v>
+        <v>-7.3536</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.47</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8875</v>
+        <v>0.8427</v>
       </c>
       <c r="J317" t="n">
-        <v>21.3</v>
+        <v>20.2248</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.21</v>
       </c>
       <c r="I318" t="n">
-        <v>0.4459</v>
+        <v>0.4426</v>
       </c>
       <c r="J318" t="n">
-        <v>10.7016</v>
+        <v>10.6224</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>0.97</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0535</v>
+        <v>-0.0608</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.284</v>
+        <v>-1.4592</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.79</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2531</v>
+        <v>-0.2655</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.0744</v>
+        <v>-6.372</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.74</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.302</v>
+        <v>-0.3136</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.248</v>
+        <v>-7.5264</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>2.03</v>
       </c>
       <c r="I322" t="n">
-        <v>1.7218</v>
+        <v>1.7256</v>
       </c>
       <c r="J322" t="n">
-        <v>29.2706</v>
+        <v>29.3352</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0145</v>
+        <v>0.9676</v>
       </c>
       <c r="J323" t="n">
-        <v>17.2465</v>
+        <v>16.4492</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.34</v>
       </c>
       <c r="I324" t="n">
-        <v>0.8447</v>
+        <v>0.8055</v>
       </c>
       <c r="J324" t="n">
-        <v>14.3599</v>
+        <v>13.6935</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>1.18</v>
       </c>
       <c r="I325" t="n">
-        <v>0.47</v>
+        <v>0.4727</v>
       </c>
       <c r="J325" t="n">
-        <v>7.99</v>
+        <v>8.0359</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>1.02</v>
       </c>
       <c r="I326" t="n">
-        <v>0.001</v>
+        <v>0.0351</v>
       </c>
       <c r="J326" t="n">
-        <v>0.017</v>
+        <v>0.5967</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.02</v>
       </c>
       <c r="I327" t="n">
-        <v>0.1745</v>
+        <v>0.1528</v>
       </c>
       <c r="J327" t="n">
-        <v>2.9665</v>
+        <v>2.5976</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>0.71</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2898</v>
+        <v>-0.3097</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.9266</v>
+        <v>-5.2649</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3079</v>
+        <v>-0.3273</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.2343</v>
+        <v>-5.5641</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.59</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4009</v>
+        <v>-0.4165</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.8153</v>
+        <v>-7.0805</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4289</v>
+        <v>-0.443</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.2913</v>
+        <v>-7.531</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.68</v>
       </c>
       <c r="I332" t="n">
-        <v>1.3475</v>
+        <v>1.3272</v>
       </c>
       <c r="J332" t="n">
-        <v>26.95</v>
+        <v>26.544</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.52</v>
       </c>
       <c r="I333" t="n">
-        <v>1.1505</v>
+        <v>1.1171</v>
       </c>
       <c r="J333" t="n">
-        <v>23.01</v>
+        <v>22.342</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1.26</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6886</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="J334" t="n">
-        <v>13.772</v>
+        <v>13.256</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>1.11</v>
       </c>
       <c r="I335" t="n">
-        <v>0.3137</v>
+        <v>0.3244</v>
       </c>
       <c r="J335" t="n">
-        <v>6.274</v>
+        <v>6.488</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.79</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.7171</v>
+        <v>-0.6597</v>
       </c>
       <c r="J336" t="n">
-        <v>-14.342</v>
+        <v>-13.194</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.24</v>
       </c>
       <c r="I337" t="n">
-        <v>0.554</v>
+        <v>0.5322</v>
       </c>
       <c r="J337" t="n">
-        <v>11.08</v>
+        <v>10.644</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.04</v>
       </c>
       <c r="I338" t="n">
-        <v>0.143</v>
+        <v>0.1441</v>
       </c>
       <c r="J338" t="n">
-        <v>2.86</v>
+        <v>2.882</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.85</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1759</v>
+        <v>-0.1921</v>
       </c>
       <c r="J339" t="n">
-        <v>-3.518</v>
+        <v>-3.842</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.68</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3427</v>
+        <v>-0.3562</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.854</v>
+        <v>-7.124</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.67</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3521</v>
+        <v>-0.3653</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.042</v>
+        <v>-7.306</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.3</v>
       </c>
       <c r="I342" t="n">
-        <v>0.6179</v>
+        <v>0.598</v>
       </c>
       <c r="J342" t="n">
-        <v>12.9759</v>
+        <v>12.558</v>
       </c>
     </row>
     <row r="343">
@@ -17949,10 +17949,10 @@
         <v>0.95</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0757</v>
+        <v>-0.0859</v>
       </c>
       <c r="J344" t="n">
-        <v>-1.5897</v>
+        <v>-1.8039</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.93</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.0998</v>
+        <v>-0.1113</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.0958</v>
+        <v>-2.3373</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2287</v>
+        <v>-0.2423</v>
       </c>
       <c r="J346" t="n">
-        <v>-4.8027</v>
+        <v>-5.0883</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.64</v>
       </c>
       <c r="I347" t="n">
-        <v>1.3568</v>
+        <v>1.327</v>
       </c>
       <c r="J347" t="n">
-        <v>28.4928</v>
+        <v>27.867</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.23</v>
       </c>
       <c r="I348" t="n">
-        <v>0.6625</v>
+        <v>0.6306</v>
       </c>
       <c r="J348" t="n">
-        <v>13.9125</v>
+        <v>13.2426</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.09</v>
       </c>
       <c r="I349" t="n">
-        <v>0.2976</v>
+        <v>0.2999</v>
       </c>
       <c r="J349" t="n">
-        <v>6.2496</v>
+        <v>6.2979</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.88</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4305</v>
+        <v>-0.4113</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.0405</v>
+        <v>-8.6373</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.59</v>
       </c>
       <c r="I351" t="n">
-        <v>-1.1605</v>
+        <v>-1.0528</v>
       </c>
       <c r="J351" t="n">
-        <v>-24.3705</v>
+        <v>-22.1088</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.17</v>
       </c>
       <c r="I352" t="n">
-        <v>0.4038</v>
+        <v>0.3971</v>
       </c>
       <c r="J352" t="n">
-        <v>11.7102</v>
+        <v>11.5159</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.09</v>
       </c>
       <c r="I353" t="n">
-        <v>0.243</v>
+        <v>0.2452</v>
       </c>
       <c r="J353" t="n">
-        <v>7.047</v>
+        <v>7.1108</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.0828</v>
+        <v>-0.095</v>
       </c>
       <c r="J354" t="n">
-        <v>-2.4012</v>
+        <v>-2.755</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>0.8</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.2316</v>
+        <v>-0.2466</v>
       </c>
       <c r="J355" t="n">
-        <v>-6.7164</v>
+        <v>-7.1514</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3385</v>
+        <v>-0.3512</v>
       </c>
       <c r="J356" t="n">
-        <v>-9.8165</v>
+        <v>-10.1848</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.54</v>
       </c>
       <c r="I357" t="n">
-        <v>1.1874</v>
+        <v>1.1544</v>
       </c>
       <c r="J357" t="n">
-        <v>34.4346</v>
+        <v>33.4776</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.5</v>
       </c>
       <c r="I358" t="n">
-        <v>1.1367</v>
+        <v>1.1</v>
       </c>
       <c r="J358" t="n">
-        <v>32.9643</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>1.08</v>
       </c>
       <c r="I359" t="n">
-        <v>0.24</v>
+        <v>0.2533</v>
       </c>
       <c r="J359" t="n">
-        <v>6.96</v>
+        <v>7.3457</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>1.06</v>
       </c>
       <c r="I360" t="n">
-        <v>0.1792</v>
+        <v>0.1963</v>
       </c>
       <c r="J360" t="n">
-        <v>5.1968</v>
+        <v>5.6927</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.92</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3494</v>
+        <v>-0.329</v>
       </c>
       <c r="J361" t="n">
-        <v>-10.1326</v>
+        <v>-9.541</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.79</v>
       </c>
       <c r="I362" t="n">
-        <v>1.4418</v>
+        <v>1.4331</v>
       </c>
       <c r="J362" t="n">
-        <v>21.627</v>
+        <v>21.4965</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.58</v>
       </c>
       <c r="I363" t="n">
-        <v>1.1962</v>
+        <v>1.1717</v>
       </c>
       <c r="J363" t="n">
-        <v>17.943</v>
+        <v>17.5755</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.55</v>
       </c>
       <c r="I364" t="n">
-        <v>1.1606</v>
+        <v>1.1333</v>
       </c>
       <c r="J364" t="n">
-        <v>17.409</v>
+        <v>16.9995</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>1.14</v>
       </c>
       <c r="I365" t="n">
-        <v>0.3608</v>
+        <v>0.375</v>
       </c>
       <c r="J365" t="n">
-        <v>5.412</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>1.07</v>
       </c>
       <c r="I366" t="n">
-        <v>0.1631</v>
+        <v>0.1925</v>
       </c>
       <c r="J366" t="n">
-        <v>2.4465</v>
+        <v>2.8875</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.19</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5604</v>
+        <v>0.5202</v>
       </c>
       <c r="J367" t="n">
-        <v>8.406000000000001</v>
+        <v>7.803</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>0.84</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.1636</v>
+        <v>-0.1852</v>
       </c>
       <c r="J368" t="n">
-        <v>-2.454</v>
+        <v>-2.778</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.75</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.2551</v>
+        <v>-0.2753</v>
       </c>
       <c r="J369" t="n">
-        <v>-3.8265</v>
+        <v>-4.1295</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.49</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4965</v>
+        <v>-0.5062</v>
       </c>
       <c r="J370" t="n">
-        <v>-7.4475</v>
+        <v>-7.593</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.37</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.6078</v>
+        <v>-0.6098</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.117000000000001</v>
+        <v>-9.147</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>2.12</v>
       </c>
       <c r="I372" t="n">
-        <v>1.8338</v>
+        <v>1.8592</v>
       </c>
       <c r="J372" t="n">
-        <v>34.8422</v>
+        <v>35.3248</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.31</v>
       </c>
       <c r="I373" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.7577</v>
       </c>
       <c r="J373" t="n">
-        <v>15.0841</v>
+        <v>14.3963</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>1.23</v>
       </c>
       <c r="I374" t="n">
-        <v>0.6132</v>
+        <v>0.5968</v>
       </c>
       <c r="J374" t="n">
-        <v>11.6508</v>
+        <v>11.3392</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.99</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1287</v>
+        <v>-0.111</v>
       </c>
       <c r="J375" t="n">
-        <v>-2.4453</v>
+        <v>-2.109</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.87</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.4747</v>
       </c>
       <c r="J376" t="n">
-        <v>-9.7394</v>
+        <v>-9.019299999999999</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.16</v>
       </c>
       <c r="I377" t="n">
-        <v>0.4192</v>
+        <v>0.4046</v>
       </c>
       <c r="J377" t="n">
-        <v>7.9648</v>
+        <v>7.6874</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.02</v>
       </c>
       <c r="I378" t="n">
-        <v>0.1044</v>
+        <v>0.1012</v>
       </c>
       <c r="J378" t="n">
-        <v>1.9836</v>
+        <v>1.9228</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>1.02</v>
       </c>
       <c r="I379" t="n">
-        <v>0.1044</v>
+        <v>0.1012</v>
       </c>
       <c r="J379" t="n">
-        <v>1.9836</v>
+        <v>1.9228</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.58</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.431</v>
+        <v>-0.4416</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.189</v>
+        <v>-8.3904</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.5</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5044</v>
+        <v>-0.5111</v>
       </c>
       <c r="J381" t="n">
-        <v>-9.583600000000001</v>
+        <v>-9.710900000000001</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.93</v>
       </c>
       <c r="I382" t="n">
-        <v>1.015</v>
+        <v>1</v>
       </c>
       <c r="J382" t="n">
-        <v>17.255</v>
+        <v>17</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.6</v>
       </c>
       <c r="I383" t="n">
-        <v>0.7015</v>
+        <v>0.7023</v>
       </c>
       <c r="J383" t="n">
-        <v>11.9255</v>
+        <v>11.9391</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.31</v>
       </c>
       <c r="I384" t="n">
-        <v>0.3959</v>
+        <v>0.4132</v>
       </c>
       <c r="J384" t="n">
-        <v>6.7303</v>
+        <v>7.0244</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.99</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.0537</v>
+        <v>-0.051</v>
       </c>
       <c r="J385" t="n">
-        <v>-0.9129</v>
+        <v>-0.867</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.93</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.1344</v>
+        <v>-0.1384</v>
       </c>
       <c r="J386" t="n">
-        <v>-2.2848</v>
+        <v>-2.3528</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.02</v>
       </c>
       <c r="I387" t="n">
-        <v>0.1178</v>
+        <v>0.1078</v>
       </c>
       <c r="J387" t="n">
-        <v>2.0026</v>
+        <v>1.8326</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>0.88</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.1236</v>
+        <v>-0.1443</v>
       </c>
       <c r="J388" t="n">
-        <v>-2.1012</v>
+        <v>-2.4531</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>0.65</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.35</v>
+        <v>-0.3671</v>
       </c>
       <c r="J389" t="n">
-        <v>-5.95</v>
+        <v>-6.2407</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.63</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3688</v>
+        <v>-0.385</v>
       </c>
       <c r="J390" t="n">
-        <v>-6.2696</v>
+        <v>-6.545</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4343</v>
+        <v>-0.4473</v>
       </c>
       <c r="J391" t="n">
-        <v>-7.3831</v>
+        <v>-7.6041</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.26</v>
       </c>
       <c r="I392" t="n">
-        <v>0.5786</v>
+        <v>0.5567</v>
       </c>
       <c r="J392" t="n">
-        <v>10.9934</v>
+        <v>10.5773</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.14</v>
       </c>
       <c r="I393" t="n">
-        <v>0.3511</v>
+        <v>0.3466</v>
       </c>
       <c r="J393" t="n">
-        <v>6.6709</v>
+        <v>6.5854</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>0.91</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.1151</v>
+        <v>-0.1294</v>
       </c>
       <c r="J394" t="n">
-        <v>-2.1869</v>
+        <v>-2.4586</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.76</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.2691</v>
+        <v>-0.284</v>
       </c>
       <c r="J395" t="n">
-        <v>-5.1129</v>
+        <v>-5.396</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.54</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4756</v>
+        <v>-0.4827</v>
       </c>
       <c r="J396" t="n">
-        <v>-9.0364</v>
+        <v>-9.1713</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.38</v>
       </c>
       <c r="I397" t="n">
-        <v>0.9677</v>
+        <v>0.91</v>
       </c>
       <c r="J397" t="n">
-        <v>18.3863</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.27</v>
       </c>
       <c r="I398" t="n">
-        <v>0.7227</v>
+        <v>0.6908</v>
       </c>
       <c r="J398" t="n">
-        <v>13.7313</v>
+        <v>13.1252</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>1.24</v>
       </c>
       <c r="I399" t="n">
-        <v>0.6528</v>
+        <v>0.6287</v>
       </c>
       <c r="J399" t="n">
-        <v>12.4032</v>
+        <v>11.9453</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>1.16</v>
       </c>
       <c r="I400" t="n">
-        <v>0.4614</v>
+        <v>0.456</v>
       </c>
       <c r="J400" t="n">
-        <v>8.7666</v>
+        <v>8.664</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.98</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.1462</v>
+        <v>-0.1359</v>
       </c>
       <c r="J401" t="n">
-        <v>-2.7778</v>
+        <v>-2.5821</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.23</v>
       </c>
       <c r="I402" t="n">
-        <v>0.5657</v>
+        <v>0.5376</v>
       </c>
       <c r="J402" t="n">
-        <v>10.7483</v>
+        <v>10.2144</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.12</v>
       </c>
       <c r="I403" t="n">
-        <v>0.3459</v>
+        <v>0.3344</v>
       </c>
       <c r="J403" t="n">
-        <v>6.5721</v>
+        <v>6.3536</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>0.86</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.1605</v>
+        <v>-0.1779</v>
       </c>
       <c r="J404" t="n">
-        <v>-3.0495</v>
+        <v>-3.3801</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.55</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.4564</v>
+        <v>-0.4661</v>
       </c>
       <c r="J405" t="n">
-        <v>-8.6716</v>
+        <v>-8.8559</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.43</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.5659</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="J406" t="n">
-        <v>-10.7521</v>
+        <v>-10.8129</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.69</v>
       </c>
       <c r="I407" t="n">
-        <v>1.3581</v>
+        <v>1.3386</v>
       </c>
       <c r="J407" t="n">
-        <v>25.8039</v>
+        <v>25.4334</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.33</v>
       </c>
       <c r="I408" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.7993</v>
       </c>
       <c r="J408" t="n">
-        <v>16.0018</v>
+        <v>15.1867</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.28</v>
       </c>
       <c r="I409" t="n">
-        <v>0.7319</v>
+        <v>0.7018</v>
       </c>
       <c r="J409" t="n">
-        <v>13.9061</v>
+        <v>13.3342</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>1.16</v>
       </c>
       <c r="I410" t="n">
-        <v>0.4459</v>
+        <v>0.4453</v>
       </c>
       <c r="J410" t="n">
-        <v>8.472099999999999</v>
+        <v>8.460699999999999</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.93</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3328</v>
+        <v>-0.3104</v>
       </c>
       <c r="J411" t="n">
-        <v>-6.3232</v>
+        <v>-5.8976</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.97</v>
       </c>
       <c r="I412" t="n">
-        <v>1.702</v>
+        <v>1.6977</v>
       </c>
       <c r="J412" t="n">
-        <v>35.742</v>
+        <v>35.6517</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.38</v>
       </c>
       <c r="I413" t="n">
-        <v>0.9569</v>
+        <v>0.9014</v>
       </c>
       <c r="J413" t="n">
-        <v>20.0949</v>
+        <v>18.9294</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.17</v>
       </c>
       <c r="I414" t="n">
-        <v>0.4784</v>
+        <v>0.4732</v>
       </c>
       <c r="J414" t="n">
-        <v>10.0464</v>
+        <v>9.937200000000001</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.97</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.1934</v>
+        <v>-0.1795</v>
       </c>
       <c r="J415" t="n">
-        <v>-4.0614</v>
+        <v>-3.7695</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.74</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.8368</v>
+        <v>-0.7664</v>
       </c>
       <c r="J416" t="n">
-        <v>-17.5728</v>
+        <v>-16.0944</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.45</v>
       </c>
       <c r="I417" t="n">
-        <v>0.8788</v>
+        <v>0.8313</v>
       </c>
       <c r="J417" t="n">
-        <v>18.4548</v>
+        <v>17.4573</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.24</v>
       </c>
       <c r="I418" t="n">
-        <v>0.517</v>
+        <v>0.5049</v>
       </c>
       <c r="J418" t="n">
-        <v>10.857</v>
+        <v>10.6029</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.85</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.1861</v>
+        <v>-0.2</v>
       </c>
       <c r="J419" t="n">
-        <v>-3.9081</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.71</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.3249</v>
+        <v>-0.337</v>
       </c>
       <c r="J420" t="n">
-        <v>-6.8229</v>
+        <v>-7.077</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.67</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3627</v>
+        <v>-0.3736</v>
       </c>
       <c r="J421" t="n">
-        <v>-7.6167</v>
+        <v>-7.8456</v>
       </c>
     </row>
     <row r="422">
@@ -21069,10 +21069,10 @@
         <v>2.34</v>
       </c>
       <c r="I422" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J422" t="n">
-        <v>36.676</v>
+        <v>38.744</v>
       </c>
     </row>
     <row r="423">
@@ -21109,10 +21109,10 @@
         <v>1.35</v>
       </c>
       <c r="I423" t="n">
-        <v>0.8985</v>
+        <v>0.8465</v>
       </c>
       <c r="J423" t="n">
-        <v>17.97</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="424">
@@ -21149,10 +21149,10 @@
         <v>0.84</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.5772</v>
+        <v>-0.5365</v>
       </c>
       <c r="J424" t="n">
-        <v>-11.544</v>
+        <v>-10.73</v>
       </c>
     </row>
     <row r="425">
@@ -21189,10 +21189,10 @@
         <v>0.83</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.6038</v>
+        <v>-0.5604</v>
       </c>
       <c r="J425" t="n">
-        <v>-12.076</v>
+        <v>-11.208</v>
       </c>
     </row>
     <row r="426">
@@ -21229,10 +21229,10 @@
         <v>0.79</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.7078</v>
+        <v>-0.6531</v>
       </c>
       <c r="J426" t="n">
-        <v>-14.156</v>
+        <v>-13.062</v>
       </c>
     </row>
     <row r="427">
@@ -21269,10 +21269,10 @@
         <v>1.5</v>
       </c>
       <c r="I427" t="n">
-        <v>1.0045</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="J427" t="n">
-        <v>20.09</v>
+        <v>18.922</v>
       </c>
     </row>
     <row r="428">
@@ -21309,10 +21309,10 @@
         <v>1.13</v>
       </c>
       <c r="I428" t="n">
-        <v>0.3442</v>
+        <v>0.3374</v>
       </c>
       <c r="J428" t="n">
-        <v>6.884</v>
+        <v>6.748</v>
       </c>
     </row>
     <row r="429">
@@ -21349,10 +21349,10 @@
         <v>0.76</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.2648</v>
+        <v>-0.2806</v>
       </c>
       <c r="J429" t="n">
-        <v>-5.296</v>
+        <v>-5.612</v>
       </c>
     </row>
     <row r="430">
@@ -21389,10 +21389,10 @@
         <v>0.58</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.435</v>
+        <v>-0.4448</v>
       </c>
       <c r="J430" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.896000000000001</v>
       </c>
     </row>
     <row r="431">
@@ -21429,10 +21429,10 @@
         <v>0.47</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.5352</v>
+        <v>-0.5395</v>
       </c>
       <c r="J431" t="n">
-        <v>-10.704</v>
+        <v>-10.79</v>
       </c>
     </row>
     <row r="432">
@@ -21469,10 +21469,10 @@
         <v>0.95</v>
       </c>
       <c r="I432" t="n">
-        <v>-0.0525</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J432" t="n">
-        <v>-0.945</v>
+        <v>-1.2258</v>
       </c>
     </row>
     <row r="433">
@@ -21509,10 +21509,10 @@
         <v>0.9</v>
       </c>
       <c r="I433" t="n">
-        <v>-0.1134</v>
+        <v>-0.1309</v>
       </c>
       <c r="J433" t="n">
-        <v>-2.0412</v>
+        <v>-2.3562</v>
       </c>
     </row>
     <row r="434">
@@ -21549,10 +21549,10 @@
         <v>0.78</v>
       </c>
       <c r="I434" t="n">
-        <v>-0.2356</v>
+        <v>-0.254</v>
       </c>
       <c r="J434" t="n">
-        <v>-4.2408</v>
+        <v>-4.572</v>
       </c>
     </row>
     <row r="435">
@@ -21589,10 +21589,10 @@
         <v>0.76</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.2548</v>
+        <v>-0.2729</v>
       </c>
       <c r="J435" t="n">
-        <v>-4.5864</v>
+        <v>-4.9122</v>
       </c>
     </row>
     <row r="436">
@@ -21629,10 +21629,10 @@
         <v>0.67</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.3407</v>
+        <v>-0.3563</v>
       </c>
       <c r="J436" t="n">
-        <v>-6.1326</v>
+        <v>-6.4134</v>
       </c>
     </row>
     <row r="437">
@@ -21669,10 +21669,10 @@
         <v>1.97</v>
       </c>
       <c r="I437" t="n">
-        <v>1.6544</v>
+        <v>1.6552</v>
       </c>
       <c r="J437" t="n">
-        <v>29.7792</v>
+        <v>29.7936</v>
       </c>
     </row>
     <row r="438">
@@ -21709,10 +21709,10 @@
         <v>1.45</v>
       </c>
       <c r="I438" t="n">
-        <v>1.0427</v>
+        <v>0.9998</v>
       </c>
       <c r="J438" t="n">
-        <v>18.7686</v>
+        <v>17.9964</v>
       </c>
     </row>
     <row r="439">
@@ -21749,10 +21749,10 @@
         <v>1.39</v>
       </c>
       <c r="I439" t="n">
-        <v>0.9484</v>
+        <v>0.899</v>
       </c>
       <c r="J439" t="n">
-        <v>17.0712</v>
+        <v>16.182</v>
       </c>
     </row>
     <row r="440">
@@ -21789,10 +21789,10 @@
         <v>1.14</v>
       </c>
       <c r="I440" t="n">
-        <v>0.3668</v>
+        <v>0.3792</v>
       </c>
       <c r="J440" t="n">
-        <v>6.6024</v>
+        <v>6.8256</v>
       </c>
     </row>
     <row r="441">
@@ -21829,10 +21829,10 @@
         <v>1.04</v>
       </c>
       <c r="I441" t="n">
-        <v>0.0732</v>
+        <v>0.1056</v>
       </c>
       <c r="J441" t="n">
-        <v>1.3176</v>
+        <v>1.9008</v>
       </c>
     </row>
     <row r="442">
@@ -21869,10 +21869,10 @@
         <v>1.2</v>
       </c>
       <c r="I442" t="n">
-        <v>0.4768</v>
+        <v>0.4617</v>
       </c>
       <c r="J442" t="n">
-        <v>13.3504</v>
+        <v>12.9276</v>
       </c>
     </row>
     <row r="443">
@@ -21909,10 +21909,10 @@
         <v>1.19</v>
       </c>
       <c r="I443" t="n">
-        <v>0.4577</v>
+        <v>0.4441</v>
       </c>
       <c r="J443" t="n">
-        <v>12.8156</v>
+        <v>12.4348</v>
       </c>
     </row>
     <row r="444">
@@ -21949,10 +21949,10 @@
         <v>0.79</v>
       </c>
       <c r="I444" t="n">
-        <v>-0.2368</v>
+        <v>-0.2528</v>
       </c>
       <c r="J444" t="n">
-        <v>-6.6304</v>
+        <v>-7.0784</v>
       </c>
     </row>
     <row r="445">
@@ -21989,10 +21989,10 @@
         <v>0.76</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.2663</v>
+        <v>-0.2818</v>
       </c>
       <c r="J445" t="n">
-        <v>-7.4564</v>
+        <v>-7.8904</v>
       </c>
     </row>
     <row r="446">
@@ -22029,10 +22029,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.4548</v>
+        <v>-0.4634</v>
       </c>
       <c r="J446" t="n">
-        <v>-12.7344</v>
+        <v>-12.9752</v>
       </c>
     </row>
     <row r="447">
@@ -22069,10 +22069,10 @@
         <v>1.86</v>
       </c>
       <c r="I447" t="n">
-        <v>1.5737</v>
+        <v>1.5636</v>
       </c>
       <c r="J447" t="n">
-        <v>44.0636</v>
+        <v>43.7808</v>
       </c>
     </row>
     <row r="448">
@@ -22109,10 +22109,10 @@
         <v>1.3</v>
       </c>
       <c r="I448" t="n">
-        <v>0.7834</v>
+        <v>0.746</v>
       </c>
       <c r="J448" t="n">
-        <v>21.9352</v>
+        <v>20.888</v>
       </c>
     </row>
     <row r="449">
@@ -22149,10 +22149,10 @@
         <v>1.14</v>
       </c>
       <c r="I449" t="n">
-        <v>0.4023</v>
+        <v>0.4038</v>
       </c>
       <c r="J449" t="n">
-        <v>11.2644</v>
+        <v>11.3064</v>
       </c>
     </row>
     <row r="450">
@@ -22189,10 +22189,10 @@
         <v>1.03</v>
       </c>
       <c r="I450" t="n">
-        <v>0.0746</v>
+        <v>0.0973</v>
       </c>
       <c r="J450" t="n">
-        <v>2.0888</v>
+        <v>2.7244</v>
       </c>
     </row>
     <row r="451">
@@ -22229,10 +22229,10 @@
         <v>0.87</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.4981</v>
+        <v>-0.4645</v>
       </c>
       <c r="J451" t="n">
-        <v>-13.9468</v>
+        <v>-13.006</v>
       </c>
     </row>
   </sheetData>
